--- a/articolo_06_trincee-drenanti-foglio/Trincee_Drenanti_v1_0.xlsx
+++ b/articolo_06_trincee-drenanti-foglio/Trincee_Drenanti_v1_0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\_Francisco\_GitHub\franciscojmendez_Risorse\articolo_06_trincee-drenanti-foglio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18B196A3-6ADE-462B-8A0D-683F3E101F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CDDDBAD-A33C-4894-9EDC-09454DFC7535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{3C2956EA-F146-457E-A9D7-5BDD1E22F3AE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{3C2956EA-F146-457E-A9D7-5BDD1E22F3AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Credits" sheetId="1" r:id="rId1"/>
@@ -853,12 +853,6 @@
     <xf numFmtId="11" fontId="15" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -870,6 +864,12 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1090,64 +1090,64 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0.45</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.9</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.35</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2.25</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.15</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3.6</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.05</c:v>
-                </c:pt>
                 <c:pt idx="9">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.25</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.75</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>4.5</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>4.95</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.4</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5.85</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>6.3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>6.75</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7.65</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>8.1</c:v>
-                </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.5500000000000007</c:v>
+                  <c:v>4.75</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1159,64 +1159,64 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>2.1622427751155429</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4344187625492677</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1918107583605089</c:v>
+                  <c:v>1.0314904613595928</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0705067562661299</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.99772435500950252</c:v>
+                  <c:v>1.0314904613595928</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.94920275417175048</c:v>
+                  <c:v>1.0314904613595928</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.91454446785907084</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.88855075312456111</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.86833341944216458</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.85215955249624742</c:v>
+                  <c:v>1.0314904613595928</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.83892638863140612</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.82789875207737129</c:v>
+                  <c:v>1.0314904613595928</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.81856767499318839</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.81056960892103158</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.80363795165849561</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.79757275155377672</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.79222110440255389</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.78746408471257845</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.78320780393733702</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.77937715123961981</c:v>
+                  <c:v>1.0314904613595928</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1261,64 +1261,64 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0.45</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.9</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.35</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2.25</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.15</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3.6</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.05</c:v>
-                </c:pt>
                 <c:pt idx="9">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.25</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.75</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>4.5</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>4.95</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.4</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5.85</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>6.3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>6.75</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7.65</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>8.1</c:v>
-                </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.5500000000000007</c:v>
+                  <c:v>4.75</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1330,64 +1330,64 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>2.9165076823335139</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.1886836697672387</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.9460756655784801</c:v>
+                  <c:v>2.1325700506890386</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8247716634841009</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.7519892622274735</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.7034676613897217</c:v>
+                  <c:v>2.1325700506890386</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.6688093750770421</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.6428156603425321</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.6225983266601358</c:v>
+                  <c:v>2.1325700506890395</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.6064244597142185</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.5931912958493772</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.5821636592953423</c:v>
+                  <c:v>2.1325700506890386</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.5728325822111595</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.5289171396048136</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.4740956469633588</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.426126840902086</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.3838014237891978</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.3461788307999645</c:v>
+                  <c:v>2.1325700506890395</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.3125165107569658</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.2822204227182672</c:v>
+                  <c:v>2.132570050689039</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1433,64 +1433,64 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0.45</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.9</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.35</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>2.25</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.15</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3.6</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.05</c:v>
-                </c:pt>
                 <c:pt idx="9">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.25</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.75</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>4.5</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>4.95</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.4</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>5.85</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>6.3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>6.75</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7.65</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>8.1</c:v>
-                </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.5500000000000007</c:v>
+                  <c:v>4.75</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1502,64 +1502,64 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>2.9165076823335139</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.1886836697672387</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.7505255044478949</c:v>
+                  <c:v>1.0314904613595928</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4895428158316695</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3329532026619342</c:v>
+                  <c:v>1.0314904613595928</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.2285601272154436</c:v>
+                  <c:v>1.0314904613595928</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.1539936447536649</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0980687829073308</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.05457166813796</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0197739763224631</c:v>
+                  <c:v>1.0314904613595928</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.99130313756432964</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.96757743859921785</c:v>
+                  <c:v>1.0314904613595928</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.94750184716720065</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.93029419736832852</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.91538090087597279</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.90233176644516155</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.89081782430032797</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.88058320906047605</c:v>
+                  <c:v>1.0314904613595932</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.87142592174060851</c:v>
+                  <c:v>1.031490461359593</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.86318436315272773</c:v>
+                  <c:v>1.0314904613595928</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2167,7 +2167,7 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1.25</c:v>
+                  <c:v>1.35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2179,7 +2179,7 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1.4245832020239257</c:v>
+                  <c:v>1.4436900037729197</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3005,10 +3005,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3020,10 +3020,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.59863853124999977</c:v>
+                  <c:v>0.55947920568839982</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.48746754375000001</c:v>
+                  <c:v>0.45662622420999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3997,13 +3997,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4015,13 +4015,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.69622806937500004</c:v>
+                  <c:v>0.66028974976300003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.60360433249999978</c:v>
+                  <c:v>0.5735879373399998</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>0.40197685124999999</c:v>
+                  <c:v>0.38189168558999992</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5140,16 +5140,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5161,16 +5161,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.70497948562500012</c:v>
+                  <c:v>0.67051290760500026</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.61116133249999993</c:v>
+                  <c:v>0.58262154653999998</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>0.40615135874999991</c:v>
+                  <c:v>0.38744974940999988</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30604324999999999</c:v>
+                  <c:v>0.29188622011999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6368,16 +6368,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6389,16 +6389,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.69403893906250014</c:v>
+                  <c:v>0.66112118264270003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.60852397999999996</c:v>
+                  <c:v>0.58040621819999993</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>0.406518555</c:v>
+                  <c:v>0.38757742711999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30491350874999995</c:v>
+                  <c:v>0.29061003300999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6933,73 +6933,73 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>2.0761361193946106E-3</c:v>
+                  <c:v>1.7445375989448208E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.306653091824741E-3</c:v>
+                  <c:v>1.8882886571193274E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.864232947672885E-3</c:v>
+                  <c:v>2.2219225192920663E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.7485714721309837E-3</c:v>
+                  <c:v>3.2465407224552766E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.9186089957851771E-3</c:v>
+                  <c:v>4.7585405324305748E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.3952991949212385E-2</c:v>
+                  <c:v>7.2536412170021219E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.8115583182409663E-2</c:v>
+                  <c:v>1.2171843193182355E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.9622859628261599E-2</c:v>
+                  <c:v>1.569705197560833E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.572060431682517E-2</c:v>
+                  <c:v>2.025908990538643E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.7962068863295597E-2</c:v>
+                  <c:v>2.6063604825222905E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.10353237615451689</c:v>
+                  <c:v>3.2265331130189472E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.13207612349263481</c:v>
+                  <c:v>3.8783950993016417E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.19430814864433679</c:v>
+                  <c:v>5.2104671486521523E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.21516454860841527</c:v>
+                  <c:v>5.6479438155163306E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.22279349184855821</c:v>
+                  <c:v>5.818517119680789E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.22410737406659911</c:v>
+                  <c:v>5.8548088461529944E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.22448404857825069</c:v>
+                  <c:v>5.8604317929106316E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.2239279978117085</c:v>
+                  <c:v>5.8311685604461705E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.22284777375884146</c:v>
+                  <c:v>5.788956539951591E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.22137408330896013</c:v>
+                  <c:v>5.7417624556015373E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.22022980762788449</c:v>
+                  <c:v>5.7163901504934236E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.21939950654332652</c:v>
+                  <c:v>5.7168750314316778E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.21921613523192873</c:v>
+                  <c:v>5.7563448341112523E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7120,79 +7120,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>3.0989125887760679E-3</c:v>
+                  <c:v>2.33037679932865E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.6317659982168034E-3</c:v>
+                  <c:v>2.6056221480398596E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.9718897945102165E-3</c:v>
+                  <c:v>4.1754631395730544E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.3052351470776389E-2</c:v>
+                  <c:v>6.7584218968357946E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.1788719566607797E-2</c:v>
+                  <c:v>1.0359307526078975E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.0745585906407521E-2</c:v>
+                  <c:v>1.3758254894933151E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.1421603277563413E-2</c:v>
+                  <c:v>1.9458733291608066E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.7993890704506958E-2</c:v>
+                  <c:v>2.8161438660117694E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.13730476983166698</c:v>
+                  <c:v>3.8759546129510193E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.18238074903569121</c:v>
+                  <c:v>4.8006238607635782E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.23702909152923068</c:v>
+                  <c:v>5.920348229472075E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2743146216448123</c:v>
+                  <c:v>6.7131208546724636E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.30494961018655997</c:v>
+                  <c:v>7.4012473341271021E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.32301248884248696</c:v>
+                  <c:v>7.8126608089828894E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.34037214805997557</c:v>
+                  <c:v>8.0988342262565433E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.34902764868080355</c:v>
+                  <c:v>8.1412674235957147E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.35439101237927623</c:v>
+                  <c:v>8.1237052906715956E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.35434469993269757</c:v>
+                  <c:v>8.0912176048058768E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.35180307277763095</c:v>
+                  <c:v>8.0582683924288884E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.34809233406504952</c:v>
+                  <c:v>8.025675840756949E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.3444462056745855</c:v>
+                  <c:v>7.9996617450096674E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.34209387490000487</c:v>
+                  <c:v>7.9854900338397941E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.34032579473122654</c:v>
+                  <c:v>7.9780313472090872E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.3408060029597702</c:v>
+                  <c:v>7.9882416427785027E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.34480225352541488</c:v>
+                  <c:v>8.0217657241966278E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7239,10 +7239,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7254,10 +7254,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.20261310391323117</c:v>
+                  <c:v>5.6070799662189405E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.31527698882290428</c:v>
+                  <c:v>7.9200150582331291E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7820,85 +7820,85 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="29"/>
                 <c:pt idx="0">
-                  <c:v>5.8699959728448312E-2</c:v>
+                  <c:v>2.1315149001949151E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.9435467375133009E-2</c:v>
+                  <c:v>2.415577092308686E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.11606187181669959</c:v>
+                  <c:v>3.5450382297405263E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.18721953644793063</c:v>
+                  <c:v>5.0736925443393852E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.28977326535010867</c:v>
+                  <c:v>7.0500086657504943E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4527414233091091</c:v>
+                  <c:v>9.8815097991484413E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.70797371897826966</c:v>
+                  <c:v>0.13880740675122266</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0428460314807526</c:v>
+                  <c:v>0.1863354916019091</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.3073476270523949</c:v>
+                  <c:v>0.22079829197131762</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.6458047026120828</c:v>
+                  <c:v>0.26070978598946309</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.0912104717920403</c:v>
+                  <c:v>0.30770424479865582</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.5227166644195322</c:v>
+                  <c:v>0.35180223300800623</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.9552561345073638</c:v>
+                  <c:v>0.39571190594675315</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.3755725537633894</c:v>
+                  <c:v>0.4391068607486705</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.6797802496988203</c:v>
+                  <c:v>0.47180740099318913</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.9419275493143173</c:v>
+                  <c:v>0.50186790201865372</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.1152301430798506</c:v>
+                  <c:v>0.52373820325414289</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.22368893922952</c:v>
+                  <c:v>0.5392937992438922</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.2745706557077998</c:v>
+                  <c:v>0.5478072452045426</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.296766151153852</c:v>
+                  <c:v>0.55193330152151998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.308453663907402</c:v>
+                  <c:v>0.55234551353827832</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.3325038217611915</c:v>
+                  <c:v>0.5483125955821665</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.375684352940775</c:v>
+                  <c:v>0.54201576557825293</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4.4102778079676064</c:v>
+                  <c:v>0.53677802151949927</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.4275416642478564</c:v>
+                  <c:v>0.53239735775268771</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4.3986971060193216</c:v>
+                  <c:v>0.53293719126834338</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4.2814893656348794</c:v>
+                  <c:v>0.54138000643902606</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8019,79 +8019,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>6.5332005076354074E-2</c:v>
+                  <c:v>2.2288049136316997E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.3024503430367991E-2</c:v>
+                  <c:v>2.706625972222966E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13029319989368909</c:v>
+                  <c:v>3.8750543756433296E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.19003663514718383</c:v>
+                  <c:v>5.1961266170191346E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.30154604169485771</c:v>
+                  <c:v>7.3630472758060408E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.45734108198958784</c:v>
+                  <c:v>9.9716767830188999E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.64880569794929766</c:v>
+                  <c:v>0.12747152694522645</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0275143347352405</c:v>
+                  <c:v>0.1740424430019672</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.5117576933089074</c:v>
+                  <c:v>0.22716519168383434</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.9766461734356795</c:v>
+                  <c:v>0.28339852259238152</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.4153043030533041</c:v>
+                  <c:v>0.33963547536073779</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.8949719502216373</c:v>
+                  <c:v>0.39752208268206068</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.442525116859056</c:v>
+                  <c:v>0.45798544754597897</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.9983191892212222</c:v>
+                  <c:v>0.51167270306086066</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.2956751269185816</c:v>
+                  <c:v>0.53612362594176088</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.5961323753895709</c:v>
+                  <c:v>0.5566428857022313</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.7310905107991932</c:v>
+                  <c:v>0.56488219014867402</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.7925392548503378</c:v>
+                  <c:v>0.56977819216090375</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.8530053009772187</c:v>
+                  <c:v>0.57711768984103151</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.8731783149623178</c:v>
+                  <c:v>0.58174177844263286</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.8762756872628295</c:v>
+                  <c:v>0.58556822398338582</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4.866547006196031</c:v>
+                  <c:v>0.58749981916318905</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.8531966770620008</c:v>
+                  <c:v>0.58776924708089962</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4.8274790127735043</c:v>
+                  <c:v>0.58527034637221975</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.8074247057332391</c:v>
+                  <c:v>0.5794087122568734</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8138,10 +8138,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8153,10 +8153,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>3.3892672929862857</c:v>
+                  <c:v>0.47036771234865554</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.7145173420375786</c:v>
+                  <c:v>0.51229916295151534</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8308,6 +8308,7 @@
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -9362,16 +9363,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9383,16 +9384,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.12505250388889821</c:v>
+                  <c:v>0.13661145225111174</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.18846199981652903</c:v>
+                  <c:v>0.20889414767112002</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>0.9350477335751991</c:v>
+                  <c:v>0.97661083453569908</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4629907179962951</c:v>
+                  <c:v>1.5047837550438994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10640,16 +10641,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10661,16 +10662,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>1.9201112403645975</c:v>
+                  <c:v>2.1680378879444366</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.6546631211364748</c:v>
+                  <c:v>2.834799394629707</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>3.8684792970592765</c:v>
+                  <c:v>4.0036154999518425</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.3971406149947496</c:v>
+                  <c:v>4.5261611730001619</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17526,11 +17527,11 @@
       </c>
       <c r="M4" s="27">
         <f>ANALISI!C50</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N4" s="27" cm="1">
         <f t="array" ref="N4">gett("T50",E$2,O$4,M4)</f>
-        <v>0.12505250388889821</v>
+        <v>0.13661145225111174</v>
       </c>
       <c r="O4" s="27">
         <v>0.5</v>
@@ -17567,11 +17568,11 @@
       </c>
       <c r="M5" s="28">
         <f>M4</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N5" s="28" cm="1">
         <f t="array" ref="N5">gett("T50",E$2,O$5,M5)</f>
-        <v>0.18846199981652903</v>
+        <v>0.20889414767112002</v>
       </c>
       <c r="O5" s="28">
         <v>1</v>
@@ -17608,11 +17609,11 @@
       </c>
       <c r="M6" s="27">
         <f>M5</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N6" s="27" cm="1">
         <f t="array" ref="N6">gett("T50",E$2,O$6,M6)</f>
-        <v>0.9350477335751991</v>
+        <v>0.97661083453569908</v>
       </c>
       <c r="O6" s="27">
         <v>1.5</v>
@@ -17649,11 +17650,11 @@
       </c>
       <c r="M7" s="28">
         <f>M6</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N7" s="28" cm="1">
         <f t="array" ref="N7">gett("T50",E$2,O$7,M7)</f>
-        <v>1.4629907179962951</v>
+        <v>1.5047837550438994</v>
       </c>
       <c r="O7" s="28">
         <v>2</v>
@@ -18437,11 +18438,11 @@
       </c>
       <c r="M4" s="27">
         <f>ANALISI!C50</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N4" s="27" cm="1">
         <f t="array" ref="N4">gett("T90",E$2,O$4,M4)</f>
-        <v>1.9201112403645975</v>
+        <v>2.1680378879444366</v>
       </c>
       <c r="O4" s="27">
         <v>0.5</v>
@@ -18478,11 +18479,11 @@
       </c>
       <c r="M5" s="28">
         <f>M4</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N5" s="28" cm="1">
         <f t="array" ref="N5">gett("T90",E$2,O$5,M5)</f>
-        <v>2.6546631211364748</v>
+        <v>2.834799394629707</v>
       </c>
       <c r="O5" s="28">
         <v>1</v>
@@ -18519,11 +18520,11 @@
       </c>
       <c r="M6" s="27">
         <f>M5</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N6" s="27" cm="1">
         <f t="array" ref="N6">gett("T90",E$2,O$6,M6)</f>
-        <v>3.8684792970592765</v>
+        <v>4.0036154999518425</v>
       </c>
       <c r="O6" s="27">
         <v>1.5</v>
@@ -18560,11 +18561,11 @@
       </c>
       <c r="M7" s="28">
         <f>M6</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N7" s="28" cm="1">
         <f t="array" ref="N7">gett("T90",E$2,O$7,M7)</f>
-        <v>4.3971406149947496</v>
+        <v>4.5261611730001619</v>
       </c>
       <c r="O7" s="28">
         <v>2</v>
@@ -19307,11 +19308,11 @@
       </c>
       <c r="E5" s="27">
         <f>ANALISI!C68</f>
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="F5" s="27">
         <f>IFERROR(getqadim(E5),"")</f>
-        <v>1.4245832020239257</v>
+        <v>1.4436900037729197</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -19513,7 +19514,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>23</v>
@@ -19526,7 +19527,7 @@
         <v>93</v>
       </c>
       <c r="B5" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>23</v>
@@ -19539,7 +19540,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>23</v>
@@ -19552,7 +19553,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>26</v>
@@ -19591,7 +19592,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="35">
-        <v>6E-9</v>
+        <v>6E-10</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>31</v>
@@ -19604,7 +19605,7 @@
         <v>32</v>
       </c>
       <c r="B11" s="35">
-        <v>6E-9</v>
+        <v>6E-10</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>31</v>
@@ -19659,7 +19660,7 @@
         <v>38</v>
       </c>
       <c r="B16" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>34</v>
@@ -19685,7 +19686,7 @@
         <v>94</v>
       </c>
       <c r="B18" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>23</v>
@@ -19716,7 +19717,7 @@
       </c>
       <c r="B20" s="21">
         <f>B6</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>23</v>
@@ -19747,7 +19748,7 @@
         <v>43</v>
       </c>
       <c r="B23" s="32">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>36</v>
@@ -19760,7 +19761,7 @@
         <v>122</v>
       </c>
       <c r="B24" s="32">
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>36</v>
@@ -19773,7 +19774,7 @@
         <v>44</v>
       </c>
       <c r="B25" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>45</v>
@@ -19804,7 +19805,7 @@
         <v>92</v>
       </c>
       <c r="B28" s="21">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>36</v>
@@ -19834,7 +19835,7 @@
         <v>132</v>
       </c>
       <c r="B30" s="21">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>36</v>
@@ -19947,27 +19948,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="P2" s="2"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
       <c r="Q3" s="4"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
@@ -19997,19 +19998,19 @@
       </c>
       <c r="D6" s="10">
         <f>DATI_INPUT!$B$4*1/20</f>
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="E6" s="10">
         <f>IFERROR(GetFZ(D6,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.1622427751155429</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="F6" s="10">
         <f>IFERROR(GetFZ(D6,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.9165076823335139</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="G6" s="10">
         <f>IFERROR(GetFZ(D6,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.9165076823335139</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
@@ -20018,343 +20019,343 @@
       </c>
       <c r="D7" s="10">
         <f>DATI_INPUT!$B$4*2/20</f>
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="10">
         <f>IFERROR(GetFZ(D7,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.4344187625492677</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="F7" s="10">
         <f>IFERROR(GetFZ(D7,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.1886836697672387</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="G7" s="10">
         <f>IFERROR(GetFZ(D7,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.1886836697672387</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D8" s="10">
         <f>DATI_INPUT!$B$4*3/20</f>
-        <v>1.35</v>
+        <v>0.75</v>
       </c>
       <c r="E8" s="10">
         <f>IFERROR(GetFZ(D8,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.1918107583605089</v>
+        <v>1.0314904613595928</v>
       </c>
       <c r="F8" s="10">
         <f>IFERROR(GetFZ(D8,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.7505255044478949</v>
+        <v>1.0314904613595928</v>
       </c>
       <c r="G8" s="10">
         <f>IFERROR(GetFZ(D8,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.9460756655784801</v>
+        <v>2.1325700506890386</v>
       </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D9" s="10">
         <f>DATI_INPUT!$B$4*4/20</f>
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="E9" s="10">
         <f>IFERROR(GetFZ(D9,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0705067562661299</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="F9" s="10">
         <f>IFERROR(GetFZ(D9,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.4895428158316695</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="G9" s="10">
         <f>IFERROR(GetFZ(D9,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.8247716634841009</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D10" s="10">
         <f>DATI_INPUT!$B$4*5/20</f>
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="E10" s="10">
         <f>IFERROR(GetFZ(D10,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.99772435500950252</v>
+        <v>1.0314904613595928</v>
       </c>
       <c r="F10" s="10">
         <f>IFERROR(GetFZ(D10,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.3329532026619342</v>
+        <v>1.0314904613595928</v>
       </c>
       <c r="G10" s="10">
         <f>IFERROR(GetFZ(D10,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.7519892622274735</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D11" s="10">
         <f>DATI_INPUT!$B$4*6/20</f>
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="E11" s="10">
         <f>IFERROR(GetFZ(D11,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.94920275417175048</v>
+        <v>1.0314904613595928</v>
       </c>
       <c r="F11" s="10">
         <f>IFERROR(GetFZ(D11,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.2285601272154436</v>
+        <v>1.0314904613595928</v>
       </c>
       <c r="G11" s="10">
         <f>IFERROR(GetFZ(D11,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.7034676613897217</v>
+        <v>2.1325700506890386</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D12" s="10">
         <f>DATI_INPUT!$B$4*7/20</f>
-        <v>3.15</v>
+        <v>1.75</v>
       </c>
       <c r="E12" s="10">
         <f>IFERROR(GetFZ(D12,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.91454446785907084</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="F12" s="10">
         <f>IFERROR(GetFZ(D12,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.1539936447536649</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="G12" s="10">
         <f>IFERROR(GetFZ(D12,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.6688093750770421</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D13" s="10">
         <f>DATI_INPUT!$B$4*8/20</f>
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="E13" s="10">
         <f>IFERROR(GetFZ(D13,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.88855075312456111</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="F13" s="10">
         <f>IFERROR(GetFZ(D13,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0980687829073308</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="G13" s="10">
         <f>IFERROR(GetFZ(D13,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.6428156603425321</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D14" s="10">
         <f>DATI_INPUT!$B$4*9/20</f>
-        <v>4.05</v>
+        <v>2.25</v>
       </c>
       <c r="E14" s="10">
         <f>IFERROR(GetFZ(D14,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.86833341944216458</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="F14" s="10">
         <f>IFERROR(GetFZ(D14,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.05457166813796</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="G14" s="10">
         <f>IFERROR(GetFZ(D14,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.6225983266601358</v>
+        <v>2.1325700506890395</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D15" s="10">
         <f>DATI_INPUT!$B$4*10/20</f>
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="E15" s="10">
         <f>IFERROR(GetFZ(D15,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.85215955249624742</v>
+        <v>1.0314904613595928</v>
       </c>
       <c r="F15" s="10">
         <f>IFERROR(GetFZ(D15,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0197739763224631</v>
+        <v>1.0314904613595928</v>
       </c>
       <c r="G15" s="10">
         <f>IFERROR(GetFZ(D15,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.6064244597142185</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D16" s="10">
         <f>DATI_INPUT!$B$4*11/20</f>
-        <v>4.95</v>
+        <v>2.75</v>
       </c>
       <c r="E16" s="10">
         <f>IFERROR(GetFZ(D16,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.83892638863140612</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="F16" s="10">
         <f>IFERROR(GetFZ(D16,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.99130313756432964</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="G16" s="10">
         <f>IFERROR(GetFZ(D16,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.5931912958493772</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D17" s="10">
         <f>DATI_INPUT!$B$4*12/20</f>
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="10">
         <f>IFERROR(GetFZ(D17,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.82789875207737129</v>
+        <v>1.0314904613595928</v>
       </c>
       <c r="F17" s="10">
         <f>IFERROR(GetFZ(D17,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.96757743859921785</v>
+        <v>1.0314904613595928</v>
       </c>
       <c r="G17" s="10">
         <f>IFERROR(GetFZ(D17,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.5821636592953423</v>
+        <v>2.1325700506890386</v>
       </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D18" s="10">
         <f>DATI_INPUT!$B$4*13/20</f>
-        <v>5.85</v>
+        <v>3.25</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(GetFZ(D18,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.81856767499318839</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="F18" s="10">
         <f>IFERROR(GetFZ(D18,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.94750184716720065</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="G18" s="10">
         <f>IFERROR(GetFZ(D18,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.5728325822111595</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D19" s="10">
         <f>DATI_INPUT!$B$4*14/20</f>
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="E19" s="10">
         <f>IFERROR(GetFZ(D19,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.81056960892103158</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="F19" s="10">
         <f>IFERROR(GetFZ(D19,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.93029419736832852</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="G19" s="10">
         <f>IFERROR(GetFZ(D19,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.5289171396048136</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D20" s="10">
         <f>DATI_INPUT!$B$4*15/20</f>
-        <v>6.75</v>
+        <v>3.75</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(GetFZ(D20,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.80363795165849561</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="F20" s="10">
         <f>IFERROR(GetFZ(D20,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.91538090087597279</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="G20" s="10">
         <f>IFERROR(GetFZ(D20,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.4740956469633588</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D21" s="10">
         <f>DATI_INPUT!$B$4*16/20</f>
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="E21" s="10">
         <f>IFERROR(GetFZ(D21,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.79757275155377672</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="F21" s="10">
         <f>IFERROR(GetFZ(D21,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.90233176644516155</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="G21" s="10">
         <f>IFERROR(GetFZ(D21,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.426126840902086</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D22" s="10">
         <f>DATI_INPUT!$B$4*17/20</f>
-        <v>7.65</v>
+        <v>4.25</v>
       </c>
       <c r="E22" s="10">
         <f>IFERROR(GetFZ(D22,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.79222110440255389</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="F22" s="10">
         <f>IFERROR(GetFZ(D22,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.89081782430032797</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="G22" s="10">
         <f>IFERROR(GetFZ(D22,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.3838014237891978</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D23" s="10">
         <f>DATI_INPUT!$B$4*18/20</f>
-        <v>8.1</v>
+        <v>4.5</v>
       </c>
       <c r="E23" s="10">
         <f>IFERROR(GetFZ(D23,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.78746408471257845</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="F23" s="10">
         <f>IFERROR(GetFZ(D23,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.88058320906047605</v>
+        <v>1.0314904613595932</v>
       </c>
       <c r="G23" s="10">
         <f>IFERROR(GetFZ(D23,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.3461788307999645</v>
+        <v>2.1325700506890395</v>
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D24" s="10">
         <f>DATI_INPUT!$B$4*19/20</f>
-        <v>8.5500000000000007</v>
+        <v>4.75</v>
       </c>
       <c r="E24" s="10">
         <f>IFERROR(GetFZ(D24,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.78320780393733702</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="F24" s="10">
         <f>IFERROR(GetFZ(D24,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.87142592174060851</v>
+        <v>1.031490461359593</v>
       </c>
       <c r="G24" s="10">
         <f>IFERROR(GetFZ(D24,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.3125165107569658</v>
+        <v>2.132570050689039</v>
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D25" s="10">
         <f>DATI_INPUT!$B$4*20/20</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E25" s="10">
         <f>IFERROR(GetFZ(D25,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.77937715123961981</v>
+        <v>1.0314904613595928</v>
       </c>
       <c r="F25" s="10">
         <f>IFERROR(GetFZ(D25,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.86318436315272773</v>
+        <v>1.0314904613595928</v>
       </c>
       <c r="G25" s="10">
         <f>IFERROR(GetFZ(D25,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.2822204227182672</v>
+        <v>2.132570050689039</v>
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
@@ -20362,14 +20363,14 @@
       <c r="M25" s="4"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B27" s="37" t="s">
+      <c r="B27" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
@@ -20377,14 +20378,14 @@
       </c>
       <c r="C29" s="5">
         <f>DATI_INPUT!$B$23</f>
-        <v>1.3</v>
-      </c>
-      <c r="D29" s="38" t="s">
+        <v>1.5</v>
+      </c>
+      <c r="D29" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
@@ -20392,14 +20393,14 @@
       </c>
       <c r="C30" s="6">
         <f>mesi_target</f>
-        <v>8</v>
-      </c>
-      <c r="D30" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
@@ -20407,24 +20408,24 @@
       </c>
       <c r="C31" s="6" t="str">
         <f>"F ≥ "&amp;F_short&amp;" raggiunto entro "&amp;DATI_INPUT!$B$25&amp;" mesi "</f>
-        <v xml:space="preserve">F ≥ 1,1 raggiunto entro 8 mesi </v>
-      </c>
-      <c r="D31" s="38" t="s">
+        <v xml:space="preserve">F ≥ 1,2 raggiunto entro 6 mesi </v>
+      </c>
+      <c r="D31" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="37" t="s">
+      <c r="B33" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="37"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
@@ -20432,14 +20433,14 @@
       </c>
       <c r="C35" s="7">
         <f>IFERROR(GetFZ(D_piano,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>0.9414791697375956</v>
-      </c>
-      <c r="D35" s="38" t="s">
+        <v>1.0314904613595928</v>
+      </c>
+      <c r="D35" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
@@ -20447,14 +20448,14 @@
       </c>
       <c r="C36" s="7">
         <f>IFERROR(GetFZ(D_piano,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.5700332590859047</v>
-      </c>
-      <c r="D36" s="38" t="s">
+        <v>2.132570050689039</v>
+      </c>
+      <c r="D36" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
@@ -20462,14 +20463,14 @@
       </c>
       <c r="C37" s="8">
         <f>C29-C35</f>
-        <v>0.35852083026240444</v>
-      </c>
-      <c r="D37" s="38" t="s">
+        <v>0.46850953864040723</v>
+      </c>
+      <c r="D37" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="39"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
@@ -20477,14 +20478,14 @@
       </c>
       <c r="C38" s="8">
         <f>C36-C35</f>
-        <v>0.62855408934830914</v>
-      </c>
-      <c r="D38" s="38" t="s">
+        <v>1.1010795893294463</v>
+      </c>
+      <c r="D38" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="39"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="37"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
@@ -20492,24 +20493,24 @@
       </c>
       <c r="C39" s="7">
         <f>C37/C38</f>
-        <v>0.5703897824197155</v>
-      </c>
-      <c r="D39" s="38" t="s">
+        <v>0.42550015746430098</v>
+      </c>
+      <c r="D39" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="37"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B41" s="37" t="s">
+      <c r="B41" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
@@ -20517,20 +20518,20 @@
       </c>
       <c r="C43" s="6" t="str">
         <f>DATI_INPUT!$B$28&amp;" / "&amp;DATI_INPUT!$B$29</f>
-        <v>1,5 / 1</v>
-      </c>
-      <c r="D43" s="38" t="s">
+        <v>1 / 1</v>
+      </c>
+      <c r="D43" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="39"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="39" t="s">
+      <c r="B44" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="C44" s="39"/>
+      <c r="C44" s="37"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
@@ -20540,14 +20541,14 @@
         <f t="array" ref="C45">IF(ISNA(getsuh0(n_cfg,d_cfg,C39)),
     "E richiesta fuori dal campo dell'abaco (E ammesso: "&amp;GetAbacoYRange("EFF",n_cfg,d_cfg)&amp;")",
     IFERROR(getsuh0(n_cfg,d_cfg,C39),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>2.7218276853933929</v>
-      </c>
-      <c r="D45" s="38" t="s">
+        <v>2.9194385307654738</v>
+      </c>
+      <c r="D45" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E45" s="39"/>
-      <c r="F45" s="39"/>
-      <c r="G45" s="39"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
@@ -20555,14 +20556,14 @@
       </c>
       <c r="C46" s="31">
         <f>IF(ISNUMBER(C45),C45*H0,C45)</f>
-        <v>16.330966112360358</v>
-      </c>
-      <c r="D46" s="38" t="s">
+        <v>14.597192653827369</v>
+      </c>
+      <c r="D46" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="E46" s="39"/>
-      <c r="F46" s="39"/>
-      <c r="G46" s="39"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B47" s="22"/>
@@ -20573,24 +20574,24 @@
       <c r="G47" s="22"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="39" t="s">
+      <c r="B48" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="39"/>
+      <c r="C48" s="37"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C49" s="9">
-        <v>15</v>
-      </c>
-      <c r="D49" s="38" t="s">
+        <v>13.5</v>
+      </c>
+      <c r="D49" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="E49" s="39"/>
-      <c r="F49" s="39"/>
-      <c r="G49" s="39"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="37"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
@@ -20598,14 +20599,14 @@
       </c>
       <c r="C50" s="6">
         <f>IFERROR(C49/H0,"")</f>
-        <v>2.5</v>
-      </c>
-      <c r="D50" s="38" t="s">
+        <v>2.7</v>
+      </c>
+      <c r="D50" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E50" s="39"/>
-      <c r="F50" s="39"/>
-      <c r="G50" s="39"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="37"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
@@ -20615,14 +20616,14 @@
         <f t="array" ref="C51">IF(ISNA(GetEfficienza(n_cfg,d_cfg,C50)),
     "S/H0 di progetto fuori dal campo dell'abaco (S/H0 ammesso: "&amp;GetAbacoXRange("EFF",n_cfg,d_cfg)&amp;")",
     IFERROR(GetEfficienza(n_cfg,d_cfg,C50),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>0.60360433249999978</v>
-      </c>
-      <c r="D51" s="38" t="s">
+        <v>0.45662622420999999</v>
+      </c>
+      <c r="D51" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E51" s="39"/>
-      <c r="F51" s="39"/>
-      <c r="G51" s="39"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
@@ -20632,20 +20633,20 @@
         <f>IF(OR(NOT(ISNUMBER(C51)),NOT(ISNUMBER(C39))),"-&gt; importa ModuloTrincee.bas",IF(C51&gt;=C39,"VERIFICATO: interasse scelto soddisfa F_target","NON VERIFICATO: ridurre interasse o rivedere F_target"))</f>
         <v>VERIFICATO: interasse scelto soddisfa F_target</v>
       </c>
-      <c r="D52" s="40"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54" s="37" t="s">
+      <c r="B54" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C54" s="37"/>
-      <c r="D54" s="37"/>
-      <c r="E54" s="37"/>
-      <c r="F54" s="37"/>
-      <c r="G54" s="37"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
@@ -20655,14 +20656,14 @@
         <f t="array" ref="C56">IF(ISNA(gett("T50",n_tempi,d_cfg,C50)),
     "S/H0 fuori dal campo dell'abaco T50 (ammesso: "&amp;GetAbacoXRange("T50",n_tempi,d_cfg)&amp;")",
     IFERROR(gett("T50",n_tempi,d_cfg,C50),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>0.18846199981652903</v>
-      </c>
-      <c r="D56" s="38" t="s">
+        <v>7.9200150582331291E-2</v>
+      </c>
+      <c r="D56" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E56" s="39"/>
-      <c r="F56" s="39"/>
-      <c r="G56" s="39"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="37"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
@@ -20672,14 +20673,14 @@
         <f t="array" ref="C57">IF(ISNA(gett("T90",n_tempi,d_cfg,C50)),
     "S/H0 fuori dal campo dell'abaco T90 (ammesso: "&amp;GetAbacoXRange("T90",n_tempi,d_cfg)&amp;")",
     IFERROR(gett("T90",n_tempi,d_cfg,C50),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>2.6546631211364748</v>
-      </c>
-      <c r="D57" s="38" t="s">
+        <v>0.51229916295151534</v>
+      </c>
+      <c r="D57" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E57" s="39"/>
-      <c r="F57" s="39"/>
-      <c r="G57" s="39"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="37"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
@@ -20687,14 +20688,14 @@
       </c>
       <c r="C58" s="23">
         <f>IFERROR(C56*(2*(1+nu)*(1-2*nu)*gammaw*D_piano^2)/(Emod*kv)/(30*86400),"")</f>
-        <v>2.1398289562501733</v>
-      </c>
-      <c r="D58" s="38" t="s">
+        <v>6.2448035398394897</v>
+      </c>
+      <c r="D58" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="E58" s="39"/>
-      <c r="F58" s="39"/>
-      <c r="G58" s="39"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
@@ -20702,14 +20703,14 @@
       </c>
       <c r="C59" s="23">
         <f>IFERROR(C57*(2*(1+nu)*(1-2*nu)*gammaw*D_piano^2)/(Emod*kv)/(30*86400),"")</f>
-        <v>30.14148752123706</v>
-      </c>
-      <c r="D59" s="38" t="s">
+        <v>40.393958884342574</v>
+      </c>
+      <c r="D59" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="E59" s="39"/>
-      <c r="F59" s="39"/>
-      <c r="G59" s="39"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="37"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
@@ -20717,14 +20718,14 @@
       </c>
       <c r="C60" s="8">
         <f>IFERROR(C51*C38,"")</f>
-        <v>0.37939797154123134</v>
-      </c>
-      <c r="D60" s="38" t="s">
+        <v>0.50278181543020239</v>
+      </c>
+      <c r="D60" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E60" s="39"/>
-      <c r="F60" s="39"/>
-      <c r="G60" s="39"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="37"/>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
@@ -20732,14 +20733,14 @@
       </c>
       <c r="C61" s="7">
         <f>IFERROR(C35+C60,"")</f>
-        <v>1.3208771412788269</v>
-      </c>
-      <c r="D61" s="38" t="s">
+        <v>1.5342722767897952</v>
+      </c>
+      <c r="D61" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
-      <c r="G61" s="39"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="37"/>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
@@ -20747,14 +20748,14 @@
       </c>
       <c r="C62" s="8">
         <f>IFERROR(C35+0.5*C60,"")</f>
-        <v>1.1311781555082112</v>
-      </c>
-      <c r="D62" s="38" t="s">
+        <v>1.2828813690746941</v>
+      </c>
+      <c r="D62" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E62" s="39"/>
-      <c r="F62" s="39"/>
-      <c r="G62" s="39"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="37"/>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
@@ -20762,14 +20763,14 @@
       </c>
       <c r="C63" s="8">
         <f>IFERROR(C35+0.9*C60,"")</f>
-        <v>1.2829373441247038</v>
-      </c>
-      <c r="D63" s="38" t="s">
+        <v>1.4839940952467749</v>
+      </c>
+      <c r="D63" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E63" s="39"/>
-      <c r="F63" s="39"/>
-      <c r="G63" s="39"/>
+      <c r="E63" s="37"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="37"/>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
@@ -20777,19 +20778,19 @@
       </c>
       <c r="C64" s="7" t="str">
         <f>IF(AND(C62 &gt;= F_short, C58 &lt;= mesi_target), "VERIFICATO", "NON verificato")</f>
-        <v>VERIFICATO</v>
+        <v>NON verificato</v>
       </c>
       <c r="D64" s="3"/>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B66" s="37" t="s">
+      <c r="B66" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
-      <c r="E66" s="37"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="37"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
+      <c r="G66" s="40"/>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
@@ -20797,14 +20798,14 @@
       </c>
       <c r="C68" s="23">
         <f>IFERROR(C49*SQRT(DATI_INPUT!$B$11/DATI_INPUT!$B$10)/(2*DATI_INPUT!$B$6),"")</f>
-        <v>1.25</v>
-      </c>
-      <c r="D68" s="38" t="s">
+        <v>1.35</v>
+      </c>
+      <c r="D68" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E68" s="39"/>
-      <c r="F68" s="39"/>
-      <c r="G68" s="39"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="37"/>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
@@ -20814,14 +20815,14 @@
         <f t="array" ref="C69">IF(ISNA(getqadim(C68)),
     "s fuori dal campo dell'abaco di portata (ammesso: "&amp;GetAbacoXRange("Q",0,0)&amp;")",
     IFERROR(getqadim(C68),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>1.4245832020239257</v>
-      </c>
-      <c r="D69" s="38" t="s">
+        <v>1.4436900037729197</v>
+      </c>
+      <c r="D69" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E69" s="39"/>
-      <c r="F69" s="39"/>
-      <c r="G69" s="39"/>
+      <c r="E69" s="37"/>
+      <c r="F69" s="37"/>
+      <c r="G69" s="37"/>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
@@ -20829,14 +20830,14 @@
       </c>
       <c r="C70" s="24">
         <f>IFERROR(C69*DATI_INPUT!$B$11*DATI_INPUT!$B$6*1000*3600,"")</f>
-        <v>0.18462598298230079</v>
-      </c>
-      <c r="D70" s="38" t="s">
+        <v>1.5591852040747534E-2</v>
+      </c>
+      <c r="D70" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="E70" s="39"/>
-      <c r="F70" s="39"/>
-      <c r="G70" s="39"/>
+      <c r="E70" s="37"/>
+      <c r="F70" s="37"/>
+      <c r="G70" s="37"/>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
@@ -20844,26 +20845,30 @@
       </c>
       <c r="C71" s="24">
         <f>IFERROR(C70*DATI_INPUT!$B$33,"")</f>
-        <v>9.2312991491150402</v>
-      </c>
-      <c r="D71" s="38" t="s">
+        <v>0.77959260203737668</v>
+      </c>
+      <c r="D71" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="E71" s="39"/>
-      <c r="F71" s="39"/>
-      <c r="G71" s="39"/>
+      <c r="E71" s="37"/>
+      <c r="F71" s="37"/>
+      <c r="G71" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="D51:G51"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D43:G43"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D46:G46"/>
-    <mergeCell ref="D49:G49"/>
-    <mergeCell ref="D50:G50"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="D30:G30"/>
     <mergeCell ref="D69:G69"/>
     <mergeCell ref="D70:G70"/>
     <mergeCell ref="D71:G71"/>
@@ -20878,19 +20883,15 @@
     <mergeCell ref="D68:G68"/>
     <mergeCell ref="D62:G62"/>
     <mergeCell ref="D63:G63"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B41:G41"/>
-    <mergeCell ref="D38:G38"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D51:G51"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D49:G49"/>
+    <mergeCell ref="D50:G50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -20995,11 +20996,11 @@
       </c>
       <c r="G4" s="27">
         <f>ANALISI!C50</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="H4" s="27" cm="1">
         <f t="array" ref="H4">GetEfficienza(B$2,I4,G4)</f>
-        <v>0.59863853124999977</v>
+        <v>0.55947920568839982</v>
       </c>
       <c r="I4" s="27">
         <v>0.5</v>
@@ -21022,11 +21023,11 @@
       </c>
       <c r="G5" s="28">
         <f>G4</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="H5" s="28" cm="1">
         <f t="array" ref="H5">GetEfficienza(B$2,I5,G5)</f>
-        <v>0.48746754375000001</v>
+        <v>0.45662622420999999</v>
       </c>
       <c r="I5" s="28">
         <v>1</v>
@@ -21556,11 +21557,11 @@
       </c>
       <c r="J4" s="27">
         <f>ANALISI!C50</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="K4" s="27" cm="1">
         <f t="array" ref="K4">GetEfficienza(B$2,L4,J4)</f>
-        <v>0.69622806937500004</v>
+        <v>0.66028974976300003</v>
       </c>
       <c r="L4" s="27">
         <v>0.5</v>
@@ -21590,11 +21591,11 @@
       </c>
       <c r="J5" s="28">
         <f>J4</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="K5" s="28" cm="1">
         <f t="array" ref="K5">GetEfficienza(B$2,L5,J5)</f>
-        <v>0.60360433249999978</v>
+        <v>0.5735879373399998</v>
       </c>
       <c r="L5" s="28">
         <v>1</v>
@@ -21624,11 +21625,11 @@
       </c>
       <c r="J6" s="27">
         <f>J5</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="K6" s="27" cm="1">
         <f t="array" ref="K6">GetEfficienza(B$2,L6,J6)</f>
-        <v>0.40197685124999999</v>
+        <v>0.38189168558999992</v>
       </c>
       <c r="L6" s="27">
         <v>1.5</v>
@@ -22241,11 +22242,11 @@
       </c>
       <c r="M4" s="30">
         <f>ANALISI!C50</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N4" s="27" cm="1">
         <f t="array" ref="N4">GetEfficienza(B$2,O4,M4)</f>
-        <v>0.70497948562500012</v>
+        <v>0.67051290760500026</v>
       </c>
       <c r="O4" s="27">
         <v>0.5</v>
@@ -22282,11 +22283,11 @@
       </c>
       <c r="M5" s="28">
         <f>M4</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N5" s="28" cm="1">
         <f t="array" ref="N5">GetEfficienza(B$2,O5,M5)</f>
-        <v>0.61116133249999993</v>
+        <v>0.58262154653999998</v>
       </c>
       <c r="O5" s="28">
         <v>1</v>
@@ -22323,11 +22324,11 @@
       </c>
       <c r="M6" s="30">
         <f>M5</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N6" s="27" cm="1">
         <f t="array" ref="N6">GetEfficienza(B$2,O6,M6)</f>
-        <v>0.40615135874999991</v>
+        <v>0.38744974940999988</v>
       </c>
       <c r="O6" s="27">
         <v>1.5</v>
@@ -22364,11 +22365,11 @@
       </c>
       <c r="M7" s="28">
         <f>M5</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N7" s="28" cm="1">
         <f t="array" ref="N7">GetEfficienza(B$2,O7,M7)</f>
-        <v>0.30604324999999999</v>
+        <v>0.29188622011999998</v>
       </c>
       <c r="O7" s="28">
         <v>2</v>
@@ -23063,11 +23064,11 @@
       </c>
       <c r="M4" s="30">
         <f>ANALISI!C50</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N4" s="27" cm="1">
         <f t="array" ref="N4">GetEfficienza(B$2,O4,M4)</f>
-        <v>0.69403893906250014</v>
+        <v>0.66112118264270003</v>
       </c>
       <c r="O4" s="27">
         <v>0.5</v>
@@ -23104,11 +23105,11 @@
       </c>
       <c r="M5" s="28">
         <f>M4</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N5" s="28" cm="1">
         <f t="array" ref="N5">GetEfficienza(B$2,O5,M5)</f>
-        <v>0.60852397999999996</v>
+        <v>0.58040621819999993</v>
       </c>
       <c r="O5" s="28">
         <v>1</v>
@@ -23145,11 +23146,11 @@
       </c>
       <c r="M6" s="30">
         <f>M5</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N6" s="27" cm="1">
         <f t="array" ref="N6">GetEfficienza(B$2,O6,M6)</f>
-        <v>0.406518555</v>
+        <v>0.38757742711999998</v>
       </c>
       <c r="O6" s="27">
         <v>1.5</v>
@@ -23186,11 +23187,11 @@
       </c>
       <c r="M7" s="28">
         <f>M5</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="N7" s="28" cm="1">
         <f t="array" ref="N7">GetEfficienza(B$2,O7,M7)</f>
-        <v>0.30491350874999995</v>
+        <v>0.29061003300999994</v>
       </c>
       <c r="O7" s="28">
         <v>2</v>
@@ -23927,11 +23928,11 @@
       </c>
       <c r="G4" s="27">
         <f>ANALISI!C50</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="H4" s="27" cm="1">
         <f t="array" ref="H4">gett("T50",E$2,I$4,G4)</f>
-        <v>0.20261310391323117</v>
+        <v>5.6070799662189405E-2</v>
       </c>
       <c r="I4" s="27">
         <v>0.5</v>
@@ -23943,22 +23944,22 @@
       </c>
       <c r="B5" cm="1">
         <f t="array" ref="B5">gett("T50",B$2,B$3,A5)</f>
-        <v>2.0761361193946106E-3</v>
+        <v>1.7445375989448208E-3</v>
       </c>
       <c r="D5">
         <v>0.50801507800000001</v>
       </c>
       <c r="E5" cm="1">
         <f t="array" ref="E5">gett("T50",E$2,E$3,D5)</f>
-        <v>3.0989125887760679E-3</v>
+        <v>2.33037679932865E-3</v>
       </c>
       <c r="G5" s="28">
         <f>G4</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="H5" s="28" cm="1">
         <f t="array" ref="H5">gett("T50",E$2,I$5,G5)</f>
-        <v>0.31527698882290428</v>
+        <v>7.9200150582331291E-2</v>
       </c>
       <c r="I5" s="28">
         <v>1</v>
@@ -23970,14 +23971,14 @@
       </c>
       <c r="B6" cm="1">
         <f t="array" ref="B6">gett("T50",B$2,B$3,A6)</f>
-        <v>2.306653091824741E-3</v>
+        <v>1.8882886571193274E-3</v>
       </c>
       <c r="D6">
         <v>0.51768684499999995</v>
       </c>
       <c r="E6" cm="1">
         <f t="array" ref="E6">gett("T50",E$2,E$3,D6)</f>
-        <v>3.6317659982168034E-3</v>
+        <v>2.6056221480398596E-3</v>
       </c>
       <c r="G6" s="25"/>
       <c r="H6" s="25"/>
@@ -23988,14 +23989,14 @@
       </c>
       <c r="B7" cm="1">
         <f t="array" ref="B7">gett("T50",B$2,B$3,A7)</f>
-        <v>2.864232947672885E-3</v>
+        <v>2.2219225192920663E-3</v>
       </c>
       <c r="D7">
         <v>0.56431970499999995</v>
       </c>
       <c r="E7" cm="1">
         <f t="array" ref="E7">gett("T50",E$2,E$3,D7)</f>
-        <v>6.9718897945102165E-3</v>
+        <v>4.1754631395730544E-3</v>
       </c>
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
@@ -24006,14 +24007,14 @@
       </c>
       <c r="B8" cm="1">
         <f t="array" ref="B8">gett("T50",B$2,B$3,A8)</f>
-        <v>4.7485714721309837E-3</v>
+        <v>3.2465407224552766E-3</v>
       </c>
       <c r="D8">
         <v>0.62724407299999996</v>
       </c>
       <c r="E8" cm="1">
         <f t="array" ref="E8">gett("T50",E$2,E$3,D8)</f>
-        <v>1.3052351470776389E-2</v>
+        <v>6.7584218968357946E-3</v>
       </c>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
@@ -24024,14 +24025,14 @@
       </c>
       <c r="B9" cm="1">
         <f t="array" ref="B9">gett("T50",B$2,B$3,A9)</f>
-        <v>7.9186089957851771E-3</v>
+        <v>4.7585405324305748E-3</v>
       </c>
       <c r="D9">
         <v>0.71169048899999998</v>
       </c>
       <c r="E9" cm="1">
         <f t="array" ref="E9">gett("T50",E$2,E$3,D9)</f>
-        <v>2.1788719566607797E-2</v>
+        <v>1.0359307526078975E-2</v>
       </c>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
@@ -24042,14 +24043,14 @@
       </c>
       <c r="B10" cm="1">
         <f t="array" ref="B10">gett("T50",B$2,B$3,A10)</f>
-        <v>1.3952991949212385E-2</v>
+        <v>7.2536412170021219E-3</v>
       </c>
       <c r="D10">
         <v>0.80694529000000004</v>
       </c>
       <c r="E10" cm="1">
         <f t="array" ref="E10">gett("T50",E$2,E$3,D10)</f>
-        <v>3.0745585906407521E-2</v>
+        <v>1.3758254894933151E-2</v>
       </c>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
@@ -24060,14 +24061,14 @@
       </c>
       <c r="B11" cm="1">
         <f t="array" ref="B11">gett("T50",B$2,B$3,A11)</f>
-        <v>2.8115583182409663E-2</v>
+        <v>1.2171843193182355E-2</v>
       </c>
       <c r="D11">
         <v>0.98214213699999997</v>
       </c>
       <c r="E11" cm="1">
         <f t="array" ref="E11">gett("T50",E$2,E$3,D11)</f>
-        <v>5.1421603277563413E-2</v>
+        <v>1.9458733291608066E-2</v>
       </c>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
@@ -24078,14 +24079,14 @@
       </c>
       <c r="B12" cm="1">
         <f t="array" ref="B12">gett("T50",B$2,B$3,A12)</f>
-        <v>3.9622859628261599E-2</v>
+        <v>1.569705197560833E-2</v>
       </c>
       <c r="D12">
         <v>1.2057083420000001</v>
       </c>
       <c r="E12" cm="1">
         <f t="array" ref="E12">gett("T50",E$2,E$3,D12)</f>
-        <v>8.7993890704506958E-2</v>
+        <v>2.8161438660117694E-2</v>
       </c>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
@@ -24096,14 +24097,14 @@
       </c>
       <c r="B13" cm="1">
         <f t="array" ref="B13">gett("T50",B$2,B$3,A13)</f>
-        <v>5.572060431682517E-2</v>
+        <v>2.025908990538643E-2</v>
       </c>
       <c r="D13">
         <v>1.4456923450000001</v>
       </c>
       <c r="E13" cm="1">
         <f t="array" ref="E13">gett("T50",E$2,E$3,D13)</f>
-        <v>0.13730476983166698</v>
+        <v>3.8759546129510193E-2</v>
       </c>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
@@ -24114,14 +24115,14 @@
       </c>
       <c r="B14" cm="1">
         <f t="array" ref="B14">gett("T50",B$2,B$3,A14)</f>
-        <v>7.7962068863295597E-2</v>
+        <v>2.6063604825222905E-2</v>
       </c>
       <c r="D14">
         <v>1.6484942460000001</v>
       </c>
       <c r="E14" cm="1">
         <f t="array" ref="E14">gett("T50",E$2,E$3,D14)</f>
-        <v>0.18238074903569121</v>
+        <v>4.8006238607635782E-2</v>
       </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
@@ -24130,14 +24131,14 @@
       </c>
       <c r="B15" cm="1">
         <f t="array" ref="B15">gett("T50",B$2,B$3,A15)</f>
-        <v>0.10353237615451689</v>
+        <v>3.2265331130189472E-2</v>
       </c>
       <c r="D15">
         <v>1.910284452</v>
       </c>
       <c r="E15" cm="1">
         <f t="array" ref="E15">gett("T50",E$2,E$3,D15)</f>
-        <v>0.23702909152923068</v>
+        <v>5.920348229472075E-2</v>
       </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
@@ -24146,14 +24147,14 @@
       </c>
       <c r="B16" cm="1">
         <f t="array" ref="B16">gett("T50",B$2,B$3,A16)</f>
-        <v>0.13207612349263481</v>
+        <v>3.8783950993016417E-2</v>
       </c>
       <c r="D16">
         <v>2.1294725780000001</v>
       </c>
       <c r="E16" cm="1">
         <f t="array" ref="E16">gett("T50",E$2,E$3,D16)</f>
-        <v>0.2743146216448123</v>
+        <v>6.7131208546724636E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -24162,14 +24163,14 @@
       </c>
       <c r="B17" cm="1">
         <f t="array" ref="B17">gett("T50",B$2,B$3,A17)</f>
-        <v>0.19430814864433679</v>
+        <v>5.2104671486521523E-2</v>
       </c>
       <c r="D17">
         <v>2.3809279910000001</v>
       </c>
       <c r="E17" cm="1">
         <f t="array" ref="E17">gett("T50",E$2,E$3,D17)</f>
-        <v>0.30494961018655997</v>
+        <v>7.4012473341271021E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -24178,14 +24179,14 @@
       </c>
       <c r="B18" cm="1">
         <f t="array" ref="B18">gett("T50",B$2,B$3,A18)</f>
-        <v>0.21516454860841527</v>
+        <v>5.6479438155163306E-2</v>
       </c>
       <c r="D18">
         <v>2.6110507919999999</v>
       </c>
       <c r="E18" cm="1">
         <f t="array" ref="E18">gett("T50",E$2,E$3,D18)</f>
-        <v>0.32301248884248696</v>
+        <v>7.8126608089828894E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -24194,14 +24195,14 @@
       </c>
       <c r="B19" cm="1">
         <f t="array" ref="B19">gett("T50",B$2,B$3,A19)</f>
-        <v>0.22279349184855821</v>
+        <v>5.818517119680789E-2</v>
       </c>
       <c r="D19">
         <v>2.9591186309999999</v>
       </c>
       <c r="E19" cm="1">
         <f t="array" ref="E19">gett("T50",E$2,E$3,D19)</f>
-        <v>0.34037214805997557</v>
+        <v>8.0988342262565433E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -24210,14 +24211,14 @@
       </c>
       <c r="B20" cm="1">
         <f t="array" ref="B20">gett("T50",B$2,B$3,A20)</f>
-        <v>0.22410737406659911</v>
+        <v>5.8548088461529944E-2</v>
       </c>
       <c r="D20">
         <v>3.2376107890000001</v>
       </c>
       <c r="E20" cm="1">
         <f t="array" ref="E20">gett("T50",E$2,E$3,D20)</f>
-        <v>0.34902764868080355</v>
+        <v>8.1412674235957147E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -24226,14 +24227,14 @@
       </c>
       <c r="B21" cm="1">
         <f t="array" ref="B21">gett("T50",B$2,B$3,A21)</f>
-        <v>0.22448404857825069</v>
+        <v>5.8604317929106316E-2</v>
       </c>
       <c r="D21">
         <v>3.612652229</v>
       </c>
       <c r="E21" cm="1">
         <f t="array" ref="E21">gett("T50",E$2,E$3,D21)</f>
-        <v>0.35439101237927623</v>
+        <v>8.1237052906715956E-2</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -24242,14 +24243,14 @@
       </c>
       <c r="B22" cm="1">
         <f t="array" ref="B22">gett("T50",B$2,B$3,A22)</f>
-        <v>0.2239279978117085</v>
+        <v>5.8311685604461705E-2</v>
       </c>
       <c r="D22">
         <v>3.960846359</v>
       </c>
       <c r="E22" cm="1">
         <f t="array" ref="E22">gett("T50",E$2,E$3,D22)</f>
-        <v>0.35434469993269757</v>
+        <v>8.0912176048058768E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -24258,14 +24259,14 @@
       </c>
       <c r="B23" cm="1">
         <f t="array" ref="B23">gett("T50",B$2,B$3,A23)</f>
-        <v>0.22284777375884146</v>
+        <v>5.788956539951591E-2</v>
       </c>
       <c r="D23">
         <v>4.2555037330000003</v>
       </c>
       <c r="E23" cm="1">
         <f t="array" ref="E23">gett("T50",E$2,E$3,D23)</f>
-        <v>0.35180307277763095</v>
+        <v>8.0582683924288884E-2</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -24274,14 +24275,14 @@
       </c>
       <c r="B24" cm="1">
         <f t="array" ref="B24">gett("T50",B$2,B$3,A24)</f>
-        <v>0.22137408330896013</v>
+        <v>5.7417624556015373E-2</v>
       </c>
       <c r="D24">
         <v>4.5500979629999998</v>
       </c>
       <c r="E24" cm="1">
         <f t="array" ref="E24">gett("T50",E$2,E$3,D24)</f>
-        <v>0.34809233406504952</v>
+        <v>8.025675840756949E-2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -24290,14 +24291,14 @@
       </c>
       <c r="B25" cm="1">
         <f t="array" ref="B25">gett("T50",B$2,B$3,A25)</f>
-        <v>0.22022980762788449</v>
+        <v>5.7163901504934236E-2</v>
       </c>
       <c r="D25">
         <v>4.828653267</v>
       </c>
       <c r="E25" cm="1">
         <f t="array" ref="E25">gett("T50",E$2,E$3,D25)</f>
-        <v>0.3444462056745855</v>
+        <v>7.9996617450096674E-2</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -24306,14 +24307,14 @@
       </c>
       <c r="B26" cm="1">
         <f t="array" ref="B26">gett("T50",B$2,B$3,A26)</f>
-        <v>0.21939950654332652</v>
+        <v>5.7168750314316778E-2</v>
       </c>
       <c r="D26">
         <v>5.0428634319999999</v>
       </c>
       <c r="E26" cm="1">
         <f t="array" ref="E26">gett("T50",E$2,E$3,D26)</f>
-        <v>0.34209387490000487</v>
+        <v>7.9854900338397941E-2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -24322,14 +24323,14 @@
       </c>
       <c r="B27" cm="1">
         <f t="array" ref="B27">gett("T50",B$2,B$3,A27)</f>
-        <v>0.21921613523192873</v>
+        <v>5.7563448341112523E-2</v>
       </c>
       <c r="D27">
         <v>5.3107050710000001</v>
       </c>
       <c r="E27" cm="1">
         <f t="array" ref="E27">gett("T50",E$2,E$3,D27)</f>
-        <v>0.34032579473122654</v>
+        <v>7.9780313472090872E-2</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -24339,7 +24340,7 @@
       </c>
       <c r="E28" cm="1">
         <f t="array" ref="E28">gett("T50",E$2,E$3,D28)</f>
-        <v>0.3408060029597702</v>
+        <v>7.9882416427785027E-2</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -24349,7 +24350,7 @@
       </c>
       <c r="E29" cm="1">
         <f t="array" ref="E29">gett("T50",E$2,E$3,D29)</f>
-        <v>0.34480225352541488</v>
+        <v>8.0217657241966278E-2</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -24472,11 +24473,11 @@
       </c>
       <c r="G4" s="27">
         <f>ANALISI!C50</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="H4" s="27" cm="1">
         <f t="array" ref="H4">gett("T90",E$2,I$4,G4)</f>
-        <v>3.3892672929862857</v>
+        <v>0.47036771234865554</v>
       </c>
       <c r="I4" s="27">
         <v>0.5</v>
@@ -24488,22 +24489,22 @@
       </c>
       <c r="B5" cm="1">
         <f t="array" ref="B5">gett("T90",B$2,B$3,A5)</f>
-        <v>5.8699959728448312E-2</v>
+        <v>2.1315149001949151E-2</v>
       </c>
       <c r="D5">
         <v>0.50947794599999996</v>
       </c>
       <c r="E5" cm="1">
         <f t="array" ref="E5">gett("T90",E$2,E$3,D5)</f>
-        <v>6.5332005076354074E-2</v>
+        <v>2.2288049136316997E-2</v>
       </c>
       <c r="G5" s="28">
         <f>G4</f>
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="H5" s="28" cm="1">
         <f t="array" ref="H5">gett("T90",E$2,I$5,G5)</f>
-        <v>3.7145173420375786</v>
+        <v>0.51229916295151534</v>
       </c>
       <c r="I5" s="28">
         <v>1</v>
@@ -24515,14 +24516,14 @@
       </c>
       <c r="B6" cm="1">
         <f t="array" ref="B6">gett("T90",B$2,B$3,A6)</f>
-        <v>6.9435467375133009E-2</v>
+        <v>2.415577092308686E-2</v>
       </c>
       <c r="D6">
         <v>0.545776013</v>
       </c>
       <c r="E6" cm="1">
         <f t="array" ref="E6">gett("T90",E$2,E$3,D6)</f>
-        <v>8.3024503430367991E-2</v>
+        <v>2.706625972222966E-2</v>
       </c>
       <c r="G6" s="25"/>
       <c r="H6" s="25"/>
@@ -24533,14 +24534,14 @@
       </c>
       <c r="B7" cm="1">
         <f t="array" ref="B7">gett("T90",B$2,B$3,A7)</f>
-        <v>0.11606187181669959</v>
+        <v>3.5450382297405263E-2</v>
       </c>
       <c r="D7">
         <v>0.61957190900000003</v>
       </c>
       <c r="E7" cm="1">
         <f t="array" ref="E7">gett("T90",E$2,E$3,D7)</f>
-        <v>0.13029319989368909</v>
+        <v>3.8750543756433296E-2</v>
       </c>
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
@@ -24551,14 +24552,14 @@
       </c>
       <c r="B8" cm="1">
         <f t="array" ref="B8">gett("T90",B$2,B$3,A8)</f>
-        <v>0.18721953644793063</v>
+        <v>5.0736925443393852E-2</v>
       </c>
       <c r="D8">
         <v>0.68823198200000002</v>
       </c>
       <c r="E8" cm="1">
         <f t="array" ref="E8">gett("T90",E$2,E$3,D8)</f>
-        <v>0.19003663514718383</v>
+        <v>5.1961266170191346E-2</v>
       </c>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
@@ -24569,14 +24570,14 @@
       </c>
       <c r="B9" cm="1">
         <f t="array" ref="B9">gett("T90",B$2,B$3,A9)</f>
-        <v>0.28977326535010867</v>
+        <v>7.0500086657504943E-2</v>
       </c>
       <c r="D9">
         <v>0.78354992800000001</v>
       </c>
       <c r="E9" cm="1">
         <f t="array" ref="E9">gett("T90",E$2,E$3,D9)</f>
-        <v>0.30154604169485771</v>
+        <v>7.3630472758060408E-2</v>
       </c>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
@@ -24587,14 +24588,14 @@
       </c>
       <c r="B10" cm="1">
         <f t="array" ref="B10">gett("T90",B$2,B$3,A10)</f>
-        <v>0.4527414233091091</v>
+        <v>9.8815097991484413E-2</v>
       </c>
       <c r="D10">
         <v>0.88447728800000003</v>
       </c>
       <c r="E10" cm="1">
         <f t="array" ref="E10">gett("T90",E$2,E$3,D10)</f>
-        <v>0.45734108198958784</v>
+        <v>9.9716767830188999E-2</v>
       </c>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
@@ -24605,14 +24606,14 @@
       </c>
       <c r="B11" cm="1">
         <f t="array" ref="B11">gett("T90",B$2,B$3,A11)</f>
-        <v>0.70797371897826966</v>
+        <v>0.13880740675122266</v>
       </c>
       <c r="D11">
         <v>0.98543622099999995</v>
       </c>
       <c r="E11" cm="1">
         <f t="array" ref="E11">gett("T90",E$2,E$3,D11)</f>
-        <v>0.64880569794929766</v>
+        <v>0.12747152694522645</v>
       </c>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
@@ -24623,14 +24624,14 @@
       </c>
       <c r="B12" cm="1">
         <f t="array" ref="B12">gett("T90",B$2,B$3,A12)</f>
-        <v>1.0428460314807526</v>
+        <v>0.1863354916019091</v>
       </c>
       <c r="D12">
         <v>1.1558129699999999</v>
       </c>
       <c r="E12" cm="1">
         <f t="array" ref="E12">gett("T90",E$2,E$3,D12)</f>
-        <v>1.0275143347352405</v>
+        <v>0.1740424430019672</v>
       </c>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
@@ -24641,14 +24642,14 @@
       </c>
       <c r="B13" cm="1">
         <f t="array" ref="B13">gett("T90",B$2,B$3,A13)</f>
-        <v>1.3073476270523949</v>
+        <v>0.22079829197131762</v>
       </c>
       <c r="D13">
         <v>1.363719122</v>
       </c>
       <c r="E13" cm="1">
         <f t="array" ref="E13">gett("T90",E$2,E$3,D13)</f>
-        <v>1.5117576933089074</v>
+        <v>0.22716519168383434</v>
       </c>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
@@ -24659,14 +24660,14 @@
       </c>
       <c r="B14" cm="1">
         <f t="array" ref="B14">gett("T90",B$2,B$3,A14)</f>
-        <v>1.6458047026120828</v>
+        <v>0.26070978598946309</v>
       </c>
       <c r="D14">
         <v>1.582528376</v>
       </c>
       <c r="E14" cm="1">
         <f t="array" ref="E14">gett("T90",E$2,E$3,D14)</f>
-        <v>1.9766461734356795</v>
+        <v>0.28339852259238152</v>
       </c>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
@@ -24675,14 +24676,14 @@
       </c>
       <c r="B15" cm="1">
         <f t="array" ref="B15">gett("T90",B$2,B$3,A15)</f>
-        <v>2.0912104717920403</v>
+        <v>0.30770424479865582</v>
       </c>
       <c r="D15">
         <v>1.801495493</v>
       </c>
       <c r="E15" cm="1">
         <f t="array" ref="E15">gett("T90",E$2,E$3,D15)</f>
-        <v>2.4153043030533041</v>
+        <v>0.33963547536073779</v>
       </c>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
@@ -24691,14 +24692,14 @@
       </c>
       <c r="B16" cm="1">
         <f t="array" ref="B16">gett("T90",B$2,B$3,A16)</f>
-        <v>2.5227166644195322</v>
+        <v>0.35180223300800623</v>
       </c>
       <c r="D16">
         <v>2.0419530859999999</v>
       </c>
       <c r="E16" cm="1">
         <f t="array" ref="E16">gett("T90",E$2,E$3,D16)</f>
-        <v>2.8949719502216373</v>
+        <v>0.39752208268206068</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -24707,14 +24708,14 @@
       </c>
       <c r="B17" cm="1">
         <f t="array" ref="B17">gett("T90",B$2,B$3,A17)</f>
-        <v>2.9552561345073638</v>
+        <v>0.39571190594675315</v>
       </c>
       <c r="D17">
         <v>2.3361368709999999</v>
       </c>
       <c r="E17" cm="1">
         <f t="array" ref="E17">gett("T90",E$2,E$3,D17)</f>
-        <v>3.442525116859056</v>
+        <v>0.45798544754597897</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -24723,14 +24724,14 @@
       </c>
       <c r="B18" cm="1">
         <f t="array" ref="B18">gett("T90",B$2,B$3,A18)</f>
-        <v>3.3755725537633894</v>
+        <v>0.4391068607486705</v>
       </c>
       <c r="D18">
         <v>2.6946657940000001</v>
       </c>
       <c r="E18" cm="1">
         <f t="array" ref="E18">gett("T90",E$2,E$3,D18)</f>
-        <v>3.9983191892212222</v>
+        <v>0.51167270306086066</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -24739,14 +24740,14 @@
       </c>
       <c r="B19" cm="1">
         <f t="array" ref="B19">gett("T90",B$2,B$3,A19)</f>
-        <v>3.6797802496988203</v>
+        <v>0.47180740099318913</v>
       </c>
       <c r="D19">
         <v>2.9462790710000002</v>
       </c>
       <c r="E19" cm="1">
         <f t="array" ref="E19">gett("T90",E$2,E$3,D19)</f>
-        <v>4.2956751269185816</v>
+        <v>0.53612362594176088</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -24755,14 +24756,14 @@
       </c>
       <c r="B20" cm="1">
         <f t="array" ref="B20">gett("T90",B$2,B$3,A20)</f>
-        <v>3.9419275493143173</v>
+        <v>0.50186790201865372</v>
       </c>
       <c r="D20">
         <v>3.321099501</v>
       </c>
       <c r="E20" cm="1">
         <f t="array" ref="E20">gett("T90",E$2,E$3,D20)</f>
-        <v>4.5961323753895709</v>
+        <v>0.5566428857022313</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -24771,14 +24772,14 @@
       </c>
       <c r="B21" cm="1">
         <f t="array" ref="B21">gett("T90",B$2,B$3,A21)</f>
-        <v>4.1152301430798506</v>
+        <v>0.52373820325414289</v>
       </c>
       <c r="D21">
         <v>3.6103368979999999</v>
       </c>
       <c r="E21" cm="1">
         <f t="array" ref="E21">gett("T90",E$2,E$3,D21)</f>
-        <v>4.7310905107991932</v>
+        <v>0.56488219014867402</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -24787,14 +24788,14 @@
       </c>
       <c r="B22" cm="1">
         <f t="array" ref="B22">gett("T90",B$2,B$3,A22)</f>
-        <v>4.22368893922952</v>
+        <v>0.5392937992438922</v>
       </c>
       <c r="D22">
         <v>3.8192533759999998</v>
       </c>
       <c r="E22" cm="1">
         <f t="array" ref="E22">gett("T90",E$2,E$3,D22)</f>
-        <v>4.7925392548503378</v>
+        <v>0.56977819216090375</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -24803,14 +24804,14 @@
       </c>
       <c r="B23" cm="1">
         <f t="array" ref="B23">gett("T90",B$2,B$3,A23)</f>
-        <v>4.2745706557077998</v>
+        <v>0.5478072452045426</v>
       </c>
       <c r="D23">
         <v>4.1567022680000001</v>
       </c>
       <c r="E23" cm="1">
         <f t="array" ref="E23">gett("T90",E$2,E$3,D23)</f>
-        <v>4.8530053009772187</v>
+        <v>0.57711768984103151</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -24819,14 +24820,14 @@
       </c>
       <c r="B24" cm="1">
         <f t="array" ref="B24">gett("T90",B$2,B$3,A24)</f>
-        <v>4.296766151153852</v>
+        <v>0.55193330152151998</v>
       </c>
       <c r="D24">
         <v>4.4084734079999999</v>
       </c>
       <c r="E24" cm="1">
         <f t="array" ref="E24">gett("T90",E$2,E$3,D24)</f>
-        <v>4.8731783149623178</v>
+        <v>0.58174177844263286</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -24835,14 +24836,14 @@
       </c>
       <c r="B25" cm="1">
         <f t="array" ref="B25">gett("T90",B$2,B$3,A25)</f>
-        <v>4.308453663907402</v>
+        <v>0.55234551353827832</v>
       </c>
       <c r="D25">
         <v>4.6869971389999998</v>
       </c>
       <c r="E25" cm="1">
         <f t="array" ref="E25">gett("T90",E$2,E$3,D25)</f>
-        <v>4.8762756872628295</v>
+        <v>0.58556822398338582</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -24851,14 +24852,14 @@
       </c>
       <c r="B26" cm="1">
         <f t="array" ref="B26">gett("T90",B$2,B$3,A26)</f>
-        <v>4.3325038217611915</v>
+        <v>0.5483125955821665</v>
       </c>
       <c r="D26">
         <v>4.9387367070000003</v>
       </c>
       <c r="E26" cm="1">
         <f t="array" ref="E26">gett("T90",E$2,E$3,D26)</f>
-        <v>4.866547006196031</v>
+        <v>0.58749981916318905</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -24867,14 +24868,14 @@
       </c>
       <c r="B27" cm="1">
         <f t="array" ref="B27">gett("T90",B$2,B$3,A27)</f>
-        <v>4.375684352940775</v>
+        <v>0.54201576557825293</v>
       </c>
       <c r="D27">
         <v>5.1422647789999996</v>
       </c>
       <c r="E27" cm="1">
         <f t="array" ref="E27">gett("T90",E$2,E$3,D27)</f>
-        <v>4.8531966770620008</v>
+        <v>0.58776924708089962</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -24883,14 +24884,14 @@
       </c>
       <c r="B28" cm="1">
         <f t="array" ref="B28">gett("T90",B$2,B$3,A28)</f>
-        <v>4.4102778079676064</v>
+        <v>0.53677802151949927</v>
       </c>
       <c r="D28">
         <v>5.4744199829999998</v>
       </c>
       <c r="E28" cm="1">
         <f t="array" ref="E28">gett("T90",E$2,E$3,D28)</f>
-        <v>4.8274790127735043</v>
+        <v>0.58527034637221975</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -24899,14 +24900,14 @@
       </c>
       <c r="B29" cm="1">
         <f t="array" ref="B29">gett("T90",B$2,B$3,A29)</f>
-        <v>4.4275416642478564</v>
+        <v>0.53239735775268771</v>
       </c>
       <c r="D29">
         <v>5.7744341910000001</v>
       </c>
       <c r="E29" cm="1">
         <f t="array" ref="E29">gett("T90",E$2,E$3,D29)</f>
-        <v>4.8074247057332391</v>
+        <v>0.5794087122568734</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -24915,7 +24916,7 @@
       </c>
       <c r="B30" cm="1">
         <f t="array" ref="B30">gett("T90",B$2,B$3,A30)</f>
-        <v>4.3986971060193216</v>
+        <v>0.53293719126834338</v>
       </c>
       <c r="D30">
         <v>5.9191000000000003</v>
@@ -24931,7 +24932,7 @@
       </c>
       <c r="B31" cm="1">
         <f t="array" ref="B31">gett("T90",B$2,B$3,A31)</f>
-        <v>4.2814893656348794</v>
+        <v>0.54138000643902606</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">

--- a/articolo_06_trincee-drenanti-foglio/Trincee_Drenanti_v1_0.xlsx
+++ b/articolo_06_trincee-drenanti-foglio/Trincee_Drenanti_v1_0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\_Francisco\_GitHub\franciscojmendez_Risorse\articolo_06_trincee-drenanti-foglio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CDDDBAD-A33C-4894-9EDC-09454DFC7535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF985399-A5D0-4678-B8ED-B0C9D548A8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{3C2956EA-F146-457E-A9D7-5BDD1E22F3AE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3C2956EA-F146-457E-A9D7-5BDD1E22F3AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Credits" sheetId="1" r:id="rId1"/>
@@ -1090,64 +1090,64 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0.25</c:v>
+                  <c:v>0.45</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.75</c:v>
+                  <c:v>1.35</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>1.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.25</c:v>
+                  <c:v>2.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.75</c:v>
+                  <c:v>3.15</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>3.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.25</c:v>
+                  <c:v>4.05</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.5</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.75</c:v>
+                  <c:v>4.95</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3</c:v>
+                  <c:v>5.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.25</c:v>
+                  <c:v>5.85</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.75</c:v>
+                  <c:v>6.75</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4</c:v>
+                  <c:v>7.2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.25</c:v>
+                  <c:v>7.65</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.5</c:v>
+                  <c:v>8.1</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.75</c:v>
+                  <c:v>8.5500000000000007</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1159,64 +1159,64 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>2.2355251605466631</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>1.4756331158763729</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0314904613595928</c:v>
+                  <c:v>1.2223357676529432</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>1.095687093541228</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0314904613595928</c:v>
+                  <c:v>1.0196978890741992</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0314904613595928</c:v>
+                  <c:v>0.96903841942951308</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>0.93285308396902322</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>0.90571408237365536</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>0.88460597002170316</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0314904613595928</c:v>
+                  <c:v>0.86771948014014111</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>0.85390326114613568</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0314904613595928</c:v>
+                  <c:v>0.84238974531779809</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>0.83264753961689697</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>0.82429707758755311</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>0.81706001049545507</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>0.81072757678986918</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>0.80514013528494044</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>0.80017352061389313</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>0.7957297074871662</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.0314904613595928</c:v>
+                  <c:v>0.79173027567311205</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1261,64 +1261,64 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0.25</c:v>
+                  <c:v>0.45</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.75</c:v>
+                  <c:v>1.35</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>1.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.25</c:v>
+                  <c:v>2.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.75</c:v>
+                  <c:v>3.15</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>3.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.25</c:v>
+                  <c:v>4.05</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.5</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.75</c:v>
+                  <c:v>4.95</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3</c:v>
+                  <c:v>5.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.25</c:v>
+                  <c:v>5.85</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.75</c:v>
+                  <c:v>6.75</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4</c:v>
+                  <c:v>7.2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.25</c:v>
+                  <c:v>7.65</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.5</c:v>
+                  <c:v>8.1</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.75</c:v>
+                  <c:v>8.5500000000000007</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1330,64 +1330,64 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>2.999553442214963</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>2.2396613975446726</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.1325700506890386</c:v>
+                  <c:v>1.9863640493212429</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>1.8597153752095277</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>1.783726170742499</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.1325700506890386</c:v>
+                  <c:v>1.7330667010978129</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>1.6968813656373229</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>1.6697423640419551</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.1325700506890395</c:v>
+                  <c:v>1.6486342516900028</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>1.6317477618084408</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>1.6179315428144354</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.1325700506890386</c:v>
+                  <c:v>1.6064180269860979</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>1.5966758212851968</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>1.5519430601287909</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>1.4961962608672772</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>1.4474178115134522</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>1.4043780032600777</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.1325700506890395</c:v>
+                  <c:v>1.3661203959237447</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>1.3318899051491309</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.132570050689039</c:v>
+                  <c:v>1.3010824634519786</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1433,64 +1433,64 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0.25</c:v>
+                  <c:v>0.45</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.75</c:v>
+                  <c:v>1.35</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>1.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.25</c:v>
+                  <c:v>2.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.5</c:v>
+                  <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.75</c:v>
+                  <c:v>3.15</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>3.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.25</c:v>
+                  <c:v>4.05</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.5</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.75</c:v>
+                  <c:v>4.95</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3</c:v>
+                  <c:v>5.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.25</c:v>
+                  <c:v>5.85</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.5</c:v>
+                  <c:v>6.3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.75</c:v>
+                  <c:v>6.75</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4</c:v>
+                  <c:v>7.2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.25</c:v>
+                  <c:v>7.65</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.5</c:v>
+                  <c:v>8.1</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.75</c:v>
+                  <c:v>8.5500000000000007</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1502,64 +1502,64 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>2.999553442214963</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>2.2396613975446726</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0314904613595928</c:v>
+                  <c:v>1.7882826429627947</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>1.5201472500236166</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0314904613595928</c:v>
+                  <c:v>1.3592660142601103</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0314904613595928</c:v>
+                  <c:v>1.252011857084439</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>1.1754017448161025</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>1.1179441606148499</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>1.0732549284583204</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0314904613595928</c:v>
+                  <c:v>1.0375035427330965</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>1.0082524089579135</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.0314904613595928</c:v>
+                  <c:v>0.98387646414526098</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>0.96325066468840126</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>0.94557140801109274</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>0.93024938555742542</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>0.91684261591046634</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>0.9050131132807967</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.0314904613595932</c:v>
+                  <c:v>0.8944979998322018</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.031490461359593</c:v>
+                  <c:v>0.885089740430827</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.0314904613595928</c:v>
+                  <c:v>0.87662230696958976</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2167,7 +2167,7 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1.35</c:v>
+                  <c:v>1.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2179,7 +2179,7 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1.4436900037729197</c:v>
+                  <c:v>1.4245832020239257</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3005,10 +3005,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3020,10 +3020,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.55947920568839982</c:v>
+                  <c:v>0.59863853124999977</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.45662622420999999</c:v>
+                  <c:v>0.48746754375000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3997,13 +3997,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4015,13 +4015,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.66028974976300003</c:v>
+                  <c:v>0.69622806937500004</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5735879373399998</c:v>
+                  <c:v>0.60360433249999978</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>0.38189168558999992</c:v>
+                  <c:v>0.40197685124999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5140,16 +5140,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5161,16 +5161,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.67051290760500026</c:v>
+                  <c:v>0.70497948562500012</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.58262154653999998</c:v>
+                  <c:v>0.61116133249999993</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>0.38744974940999988</c:v>
+                  <c:v>0.40615135874999991</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.29188622011999998</c:v>
+                  <c:v>0.30604324999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6368,16 +6368,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6389,16 +6389,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.66112118264270003</c:v>
+                  <c:v>0.69403893906250014</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.58040621819999993</c:v>
+                  <c:v>0.60852397999999996</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>0.38757742711999998</c:v>
+                  <c:v>0.406518555</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.29061003300999994</c:v>
+                  <c:v>0.30491350874999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7239,10 +7239,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7254,10 +7254,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>5.6070799662189405E-2</c:v>
+                  <c:v>5.3837298147770163E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.9200150582331291E-2</c:v>
+                  <c:v>7.6393315101689729E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8138,10 +8138,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8153,10 +8153,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.47036771234865554</c:v>
+                  <c:v>0.44054769468300675</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.51229916295151534</c:v>
+                  <c:v>0.48537651044101932</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9363,16 +9363,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9384,16 +9384,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.13661145225111174</c:v>
+                  <c:v>0.12505250388889821</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.20889414767112002</c:v>
+                  <c:v>0.18846199981652903</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>0.97661083453569908</c:v>
+                  <c:v>0.9350477335751991</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.5047837550438994</c:v>
+                  <c:v>1.4629907179962951</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10641,16 +10641,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.7</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10662,16 +10662,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.1680378879444366</c:v>
+                  <c:v>1.9201112403645975</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.834799394629707</c:v>
+                  <c:v>2.6546631211364748</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>4.0036154999518425</c:v>
+                  <c:v>3.8684792970592765</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.5261611730001619</c:v>
+                  <c:v>4.3971406149947496</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17527,11 +17527,11 @@
       </c>
       <c r="M4" s="27">
         <f>ANALISI!C50</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N4" s="27" cm="1">
         <f t="array" ref="N4">gett("T50",E$2,O$4,M4)</f>
-        <v>0.13661145225111174</v>
+        <v>0.12505250388889821</v>
       </c>
       <c r="O4" s="27">
         <v>0.5</v>
@@ -17568,11 +17568,11 @@
       </c>
       <c r="M5" s="28">
         <f>M4</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N5" s="28" cm="1">
         <f t="array" ref="N5">gett("T50",E$2,O$5,M5)</f>
-        <v>0.20889414767112002</v>
+        <v>0.18846199981652903</v>
       </c>
       <c r="O5" s="28">
         <v>1</v>
@@ -17609,11 +17609,11 @@
       </c>
       <c r="M6" s="27">
         <f>M5</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N6" s="27" cm="1">
         <f t="array" ref="N6">gett("T50",E$2,O$6,M6)</f>
-        <v>0.97661083453569908</v>
+        <v>0.9350477335751991</v>
       </c>
       <c r="O6" s="27">
         <v>1.5</v>
@@ -17650,11 +17650,11 @@
       </c>
       <c r="M7" s="28">
         <f>M6</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N7" s="28" cm="1">
         <f t="array" ref="N7">gett("T50",E$2,O$7,M7)</f>
-        <v>1.5047837550438994</v>
+        <v>1.4629907179962951</v>
       </c>
       <c r="O7" s="28">
         <v>2</v>
@@ -18438,11 +18438,11 @@
       </c>
       <c r="M4" s="27">
         <f>ANALISI!C50</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N4" s="27" cm="1">
         <f t="array" ref="N4">gett("T90",E$2,O$4,M4)</f>
-        <v>2.1680378879444366</v>
+        <v>1.9201112403645975</v>
       </c>
       <c r="O4" s="27">
         <v>0.5</v>
@@ -18479,11 +18479,11 @@
       </c>
       <c r="M5" s="28">
         <f>M4</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N5" s="28" cm="1">
         <f t="array" ref="N5">gett("T90",E$2,O$5,M5)</f>
-        <v>2.834799394629707</v>
+        <v>2.6546631211364748</v>
       </c>
       <c r="O5" s="28">
         <v>1</v>
@@ -18520,11 +18520,11 @@
       </c>
       <c r="M6" s="27">
         <f>M5</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N6" s="27" cm="1">
         <f t="array" ref="N6">gett("T90",E$2,O$6,M6)</f>
-        <v>4.0036154999518425</v>
+        <v>3.8684792970592765</v>
       </c>
       <c r="O6" s="27">
         <v>1.5</v>
@@ -18561,11 +18561,11 @@
       </c>
       <c r="M7" s="28">
         <f>M6</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N7" s="28" cm="1">
         <f t="array" ref="N7">gett("T90",E$2,O$7,M7)</f>
-        <v>4.5261611730001619</v>
+        <v>4.3971406149947496</v>
       </c>
       <c r="O7" s="28">
         <v>2</v>
@@ -19308,11 +19308,11 @@
       </c>
       <c r="E5" s="27">
         <f>ANALISI!C68</f>
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="F5" s="27">
         <f>IFERROR(getqadim(E5),"")</f>
-        <v>1.4436900037729197</v>
+        <v>1.4245832020239257</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -19514,7 +19514,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>23</v>
@@ -19527,7 +19527,7 @@
         <v>93</v>
       </c>
       <c r="B5" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>23</v>
@@ -19540,7 +19540,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>23</v>
@@ -19553,7 +19553,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>26</v>
@@ -19592,7 +19592,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="35">
-        <v>6E-10</v>
+        <v>5.9999999999999995E-8</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>31</v>
@@ -19605,7 +19605,7 @@
         <v>32</v>
       </c>
       <c r="B11" s="35">
-        <v>6E-10</v>
+        <v>5.9999999999999995E-8</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>31</v>
@@ -19660,7 +19660,7 @@
         <v>38</v>
       </c>
       <c r="B16" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>34</v>
@@ -19673,7 +19673,7 @@
         <v>39</v>
       </c>
       <c r="B17" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>26</v>
@@ -19686,7 +19686,7 @@
         <v>94</v>
       </c>
       <c r="B18" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>23</v>
@@ -19717,7 +19717,7 @@
       </c>
       <c r="B20" s="21">
         <f>B6</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>23</v>
@@ -19748,7 +19748,7 @@
         <v>43</v>
       </c>
       <c r="B23" s="32">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>36</v>
@@ -19761,7 +19761,7 @@
         <v>122</v>
       </c>
       <c r="B24" s="32">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>36</v>
@@ -19805,7 +19805,7 @@
         <v>92</v>
       </c>
       <c r="B28" s="21">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>36</v>
@@ -19835,7 +19835,7 @@
         <v>132</v>
       </c>
       <c r="B30" s="21">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>36</v>
@@ -19998,19 +19998,19 @@
       </c>
       <c r="D6" s="10">
         <f>DATI_INPUT!$B$4*1/20</f>
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="E6" s="10">
         <f>IFERROR(GetFZ(D6,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>2.2355251605466631</v>
       </c>
       <c r="F6" s="10">
         <f>IFERROR(GetFZ(D6,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>2.999553442214963</v>
       </c>
       <c r="G6" s="10">
         <f>IFERROR(GetFZ(D6,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>2.999553442214963</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
@@ -20019,343 +20019,343 @@
       </c>
       <c r="D7" s="10">
         <f>DATI_INPUT!$B$4*2/20</f>
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E7" s="10">
         <f>IFERROR(GetFZ(D7,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>1.4756331158763729</v>
       </c>
       <c r="F7" s="10">
         <f>IFERROR(GetFZ(D7,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>2.2396613975446726</v>
       </c>
       <c r="G7" s="10">
         <f>IFERROR(GetFZ(D7,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>2.2396613975446726</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D8" s="10">
         <f>DATI_INPUT!$B$4*3/20</f>
-        <v>0.75</v>
+        <v>1.35</v>
       </c>
       <c r="E8" s="10">
         <f>IFERROR(GetFZ(D8,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595928</v>
+        <v>1.2223357676529432</v>
       </c>
       <c r="F8" s="10">
         <f>IFERROR(GetFZ(D8,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595928</v>
+        <v>1.7882826429627947</v>
       </c>
       <c r="G8" s="10">
         <f>IFERROR(GetFZ(D8,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.1325700506890386</v>
+        <v>1.9863640493212429</v>
       </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D9" s="10">
         <f>DATI_INPUT!$B$4*4/20</f>
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E9" s="10">
         <f>IFERROR(GetFZ(D9,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>1.095687093541228</v>
       </c>
       <c r="F9" s="10">
         <f>IFERROR(GetFZ(D9,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>1.5201472500236166</v>
       </c>
       <c r="G9" s="10">
         <f>IFERROR(GetFZ(D9,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.8597153752095277</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D10" s="10">
         <f>DATI_INPUT!$B$4*5/20</f>
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="E10" s="10">
         <f>IFERROR(GetFZ(D10,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595928</v>
+        <v>1.0196978890741992</v>
       </c>
       <c r="F10" s="10">
         <f>IFERROR(GetFZ(D10,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595928</v>
+        <v>1.3592660142601103</v>
       </c>
       <c r="G10" s="10">
         <f>IFERROR(GetFZ(D10,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.783726170742499</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D11" s="10">
         <f>DATI_INPUT!$B$4*6/20</f>
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="E11" s="10">
         <f>IFERROR(GetFZ(D11,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595928</v>
+        <v>0.96903841942951308</v>
       </c>
       <c r="F11" s="10">
         <f>IFERROR(GetFZ(D11,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595928</v>
+        <v>1.252011857084439</v>
       </c>
       <c r="G11" s="10">
         <f>IFERROR(GetFZ(D11,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.1325700506890386</v>
+        <v>1.7330667010978129</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D12" s="10">
         <f>DATI_INPUT!$B$4*7/20</f>
-        <v>1.75</v>
+        <v>3.15</v>
       </c>
       <c r="E12" s="10">
         <f>IFERROR(GetFZ(D12,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>0.93285308396902322</v>
       </c>
       <c r="F12" s="10">
         <f>IFERROR(GetFZ(D12,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>1.1754017448161025</v>
       </c>
       <c r="G12" s="10">
         <f>IFERROR(GetFZ(D12,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.6968813656373229</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D13" s="10">
         <f>DATI_INPUT!$B$4*8/20</f>
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="E13" s="10">
         <f>IFERROR(GetFZ(D13,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>0.90571408237365536</v>
       </c>
       <c r="F13" s="10">
         <f>IFERROR(GetFZ(D13,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>1.1179441606148499</v>
       </c>
       <c r="G13" s="10">
         <f>IFERROR(GetFZ(D13,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.6697423640419551</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D14" s="10">
         <f>DATI_INPUT!$B$4*9/20</f>
-        <v>2.25</v>
+        <v>4.05</v>
       </c>
       <c r="E14" s="10">
         <f>IFERROR(GetFZ(D14,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>0.88460597002170316</v>
       </c>
       <c r="F14" s="10">
         <f>IFERROR(GetFZ(D14,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>1.0732549284583204</v>
       </c>
       <c r="G14" s="10">
         <f>IFERROR(GetFZ(D14,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.1325700506890395</v>
+        <v>1.6486342516900028</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D15" s="10">
         <f>DATI_INPUT!$B$4*10/20</f>
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="E15" s="10">
         <f>IFERROR(GetFZ(D15,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595928</v>
+        <v>0.86771948014014111</v>
       </c>
       <c r="F15" s="10">
         <f>IFERROR(GetFZ(D15,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595928</v>
+        <v>1.0375035427330965</v>
       </c>
       <c r="G15" s="10">
         <f>IFERROR(GetFZ(D15,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.6317477618084408</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D16" s="10">
         <f>DATI_INPUT!$B$4*11/20</f>
-        <v>2.75</v>
+        <v>4.95</v>
       </c>
       <c r="E16" s="10">
         <f>IFERROR(GetFZ(D16,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>0.85390326114613568</v>
       </c>
       <c r="F16" s="10">
         <f>IFERROR(GetFZ(D16,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>1.0082524089579135</v>
       </c>
       <c r="G16" s="10">
         <f>IFERROR(GetFZ(D16,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.6179315428144354</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D17" s="10">
         <f>DATI_INPUT!$B$4*12/20</f>
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="E17" s="10">
         <f>IFERROR(GetFZ(D17,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595928</v>
+        <v>0.84238974531779809</v>
       </c>
       <c r="F17" s="10">
         <f>IFERROR(GetFZ(D17,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595928</v>
+        <v>0.98387646414526098</v>
       </c>
       <c r="G17" s="10">
         <f>IFERROR(GetFZ(D17,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.1325700506890386</v>
+        <v>1.6064180269860979</v>
       </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D18" s="10">
         <f>DATI_INPUT!$B$4*13/20</f>
-        <v>3.25</v>
+        <v>5.85</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(GetFZ(D18,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>0.83264753961689697</v>
       </c>
       <c r="F18" s="10">
         <f>IFERROR(GetFZ(D18,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>0.96325066468840126</v>
       </c>
       <c r="G18" s="10">
         <f>IFERROR(GetFZ(D18,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.5966758212851968</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D19" s="10">
         <f>DATI_INPUT!$B$4*14/20</f>
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="E19" s="10">
         <f>IFERROR(GetFZ(D19,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>0.82429707758755311</v>
       </c>
       <c r="F19" s="10">
         <f>IFERROR(GetFZ(D19,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>0.94557140801109274</v>
       </c>
       <c r="G19" s="10">
         <f>IFERROR(GetFZ(D19,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.5519430601287909</v>
       </c>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D20" s="10">
         <f>DATI_INPUT!$B$4*15/20</f>
-        <v>3.75</v>
+        <v>6.75</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(GetFZ(D20,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>0.81706001049545507</v>
       </c>
       <c r="F20" s="10">
         <f>IFERROR(GetFZ(D20,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>0.93024938555742542</v>
       </c>
       <c r="G20" s="10">
         <f>IFERROR(GetFZ(D20,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.4961962608672772</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D21" s="10">
         <f>DATI_INPUT!$B$4*16/20</f>
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="E21" s="10">
         <f>IFERROR(GetFZ(D21,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>0.81072757678986918</v>
       </c>
       <c r="F21" s="10">
         <f>IFERROR(GetFZ(D21,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>0.91684261591046634</v>
       </c>
       <c r="G21" s="10">
         <f>IFERROR(GetFZ(D21,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.4474178115134522</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D22" s="10">
         <f>DATI_INPUT!$B$4*17/20</f>
-        <v>4.25</v>
+        <v>7.65</v>
       </c>
       <c r="E22" s="10">
         <f>IFERROR(GetFZ(D22,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>0.80514013528494044</v>
       </c>
       <c r="F22" s="10">
         <f>IFERROR(GetFZ(D22,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>0.9050131132807967</v>
       </c>
       <c r="G22" s="10">
         <f>IFERROR(GetFZ(D22,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.4043780032600777</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D23" s="10">
         <f>DATI_INPUT!$B$4*18/20</f>
-        <v>4.5</v>
+        <v>8.1</v>
       </c>
       <c r="E23" s="10">
         <f>IFERROR(GetFZ(D23,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>0.80017352061389313</v>
       </c>
       <c r="F23" s="10">
         <f>IFERROR(GetFZ(D23,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595932</v>
+        <v>0.8944979998322018</v>
       </c>
       <c r="G23" s="10">
         <f>IFERROR(GetFZ(D23,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.1325700506890395</v>
+        <v>1.3661203959237447</v>
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D24" s="10">
         <f>DATI_INPUT!$B$4*19/20</f>
-        <v>4.75</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="E24" s="10">
         <f>IFERROR(GetFZ(D24,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>0.7957297074871662</v>
       </c>
       <c r="F24" s="10">
         <f>IFERROR(GetFZ(D24,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.031490461359593</v>
+        <v>0.885089740430827</v>
       </c>
       <c r="G24" s="10">
         <f>IFERROR(GetFZ(D24,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.3318899051491309</v>
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D25" s="10">
         <f>DATI_INPUT!$B$4*20/20</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E25" s="10">
         <f>IFERROR(GetFZ(D25,dw_sat,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595928</v>
+        <v>0.79173027567311205</v>
       </c>
       <c r="F25" s="10">
         <f>IFERROR(GetFZ(D25,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595928</v>
+        <v>0.87662230696958976</v>
       </c>
       <c r="G25" s="10">
         <f>IFERROR(GetFZ(D25,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.3010824634519786</v>
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
@@ -20378,7 +20378,7 @@
       </c>
       <c r="C29" s="5">
         <f>DATI_INPUT!$B$23</f>
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="D29" s="36" t="s">
         <v>36</v>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="C31" s="6" t="str">
         <f>"F ≥ "&amp;F_short&amp;" raggiunto entro "&amp;DATI_INPUT!$B$25&amp;" mesi "</f>
-        <v xml:space="preserve">F ≥ 1,2 raggiunto entro 6 mesi </v>
+        <v xml:space="preserve">F ≥ 1,1 raggiunto entro 6 mesi </v>
       </c>
       <c r="D31" s="36" t="s">
         <v>61</v>
@@ -20433,7 +20433,7 @@
       </c>
       <c r="C35" s="7">
         <f>IFERROR(GetFZ(D_piano,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>1.0314904613595928</v>
+        <v>0.95706292485134314</v>
       </c>
       <c r="D35" s="36" t="s">
         <v>36</v>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C36" s="7">
         <f>IFERROR(GetFZ(D_piano,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
-        <v>2.132570050689039</v>
+        <v>1.5937531595749261</v>
       </c>
       <c r="D36" s="36" t="s">
         <v>36</v>
@@ -20463,7 +20463,7 @@
       </c>
       <c r="C37" s="8">
         <f>C29-C35</f>
-        <v>0.46850953864040723</v>
+        <v>0.3429370751486569</v>
       </c>
       <c r="D37" s="36" t="s">
         <v>36</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C38" s="8">
         <f>C36-C35</f>
-        <v>1.1010795893294463</v>
+        <v>0.63669023472358299</v>
       </c>
       <c r="D38" s="36" t="s">
         <v>36</v>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="C39" s="7">
         <f>C37/C38</f>
-        <v>0.42550015746430098</v>
+        <v>0.53862468190287527</v>
       </c>
       <c r="D39" s="36" t="s">
         <v>36</v>
@@ -20518,7 +20518,7 @@
       </c>
       <c r="C43" s="6" t="str">
         <f>DATI_INPUT!$B$28&amp;" / "&amp;DATI_INPUT!$B$29</f>
-        <v>1 / 1</v>
+        <v>1,5 / 1</v>
       </c>
       <c r="D43" s="36" t="s">
         <v>69</v>
@@ -20541,7 +20541,7 @@
         <f t="array" ref="C45">IF(ISNA(getsuh0(n_cfg,d_cfg,C39)),
     "E richiesta fuori dal campo dell'abaco (E ammesso: "&amp;GetAbacoYRange("EFF",n_cfg,d_cfg)&amp;")",
     IFERROR(getsuh0(n_cfg,d_cfg,C39),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>2.9194385307654738</v>
+        <v>2.9446791221275923</v>
       </c>
       <c r="D45" s="36" t="s">
         <v>36</v>
@@ -20550,13 +20550,13 @@
       <c r="F45" s="37"/>
       <c r="G45" s="37"/>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>116</v>
       </c>
       <c r="C46" s="31">
         <f>IF(ISNUMBER(C45),C45*H0,C45)</f>
-        <v>14.597192653827369</v>
+        <v>17.668074732765554</v>
       </c>
       <c r="D46" s="36" t="s">
         <v>23</v>
@@ -20584,7 +20584,7 @@
         <v>103</v>
       </c>
       <c r="C49" s="9">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="D49" s="36" t="s">
         <v>23</v>
@@ -20599,7 +20599,7 @@
       </c>
       <c r="C50" s="6">
         <f>IFERROR(C49/H0,"")</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="D50" s="36" t="s">
         <v>36</v>
@@ -20616,7 +20616,7 @@
         <f t="array" ref="C51">IF(ISNA(GetEfficienza(n_cfg,d_cfg,C50)),
     "S/H0 di progetto fuori dal campo dell'abaco (S/H0 ammesso: "&amp;GetAbacoXRange("EFF",n_cfg,d_cfg)&amp;")",
     IFERROR(GetEfficienza(n_cfg,d_cfg,C50),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>0.45662622420999999</v>
+        <v>0.60360433249999978</v>
       </c>
       <c r="D51" s="36" t="s">
         <v>36</v>
@@ -20656,7 +20656,7 @@
         <f t="array" ref="C56">IF(ISNA(gett("T50",n_tempi,d_cfg,C50)),
     "S/H0 fuori dal campo dell'abaco T50 (ammesso: "&amp;GetAbacoXRange("T50",n_tempi,d_cfg)&amp;")",
     IFERROR(gett("T50",n_tempi,d_cfg,C50),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>7.9200150582331291E-2</v>
+        <v>0.18846199981652903</v>
       </c>
       <c r="D56" s="36" t="s">
         <v>36</v>
@@ -20673,7 +20673,7 @@
         <f t="array" ref="C57">IF(ISNA(gett("T90",n_tempi,d_cfg,C50)),
     "S/H0 fuori dal campo dell'abaco T90 (ammesso: "&amp;GetAbacoXRange("T90",n_tempi,d_cfg)&amp;")",
     IFERROR(gett("T90",n_tempi,d_cfg,C50),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>0.51229916295151534</v>
+        <v>2.6546631211364748</v>
       </c>
       <c r="D57" s="36" t="s">
         <v>36</v>
@@ -20687,8 +20687,8 @@
         <v>71</v>
       </c>
       <c r="C58" s="23">
-        <f>IFERROR(C56*(2*(1+nu)*(1-2*nu)*gammaw*D_piano^2)/(Emod*kv)/(30*86400),"")</f>
-        <v>6.2448035398394897</v>
+        <f>IFERROR(C56*(2*(1+nu)*(1-2*nu)*gammaw*H0^2)/(Emod*kv)/(30*86400),"")</f>
+        <v>0.21398289562501735</v>
       </c>
       <c r="D58" s="36" t="s">
         <v>45</v>
@@ -20702,8 +20702,8 @@
         <v>72</v>
       </c>
       <c r="C59" s="23">
-        <f>IFERROR(C57*(2*(1+nu)*(1-2*nu)*gammaw*D_piano^2)/(Emod*kv)/(30*86400),"")</f>
-        <v>40.393958884342574</v>
+        <f>IFERROR(C57*(2*(1+nu)*(1-2*nu)*gammaw*H0^2)/(Emod*kv)/(30*86400),"")</f>
+        <v>3.0141487521237069</v>
       </c>
       <c r="D59" s="36" t="s">
         <v>45</v>
@@ -20718,7 +20718,7 @@
       </c>
       <c r="C60" s="8">
         <f>IFERROR(C51*C38,"")</f>
-        <v>0.50278181543020239</v>
+        <v>0.38430898413959652</v>
       </c>
       <c r="D60" s="36" t="s">
         <v>36</v>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="C61" s="7">
         <f>IFERROR(C35+C60,"")</f>
-        <v>1.5342722767897952</v>
+        <v>1.3413719089909397</v>
       </c>
       <c r="D61" s="36" t="s">
         <v>36</v>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C62" s="8">
         <f>IFERROR(C35+0.5*C60,"")</f>
-        <v>1.2828813690746941</v>
+        <v>1.1492174169211413</v>
       </c>
       <c r="D62" s="36" t="s">
         <v>36</v>
@@ -20763,7 +20763,7 @@
       </c>
       <c r="C63" s="8">
         <f>IFERROR(C35+0.9*C60,"")</f>
-        <v>1.4839940952467749</v>
+        <v>1.3029410105769801</v>
       </c>
       <c r="D63" s="36" t="s">
         <v>36</v>
@@ -20778,7 +20778,7 @@
       </c>
       <c r="C64" s="7" t="str">
         <f>IF(AND(C62 &gt;= F_short, C58 &lt;= mesi_target), "VERIFICATO", "NON verificato")</f>
-        <v>NON verificato</v>
+        <v>VERIFICATO</v>
       </c>
       <c r="D64" s="3"/>
     </row>
@@ -20798,7 +20798,7 @@
       </c>
       <c r="C68" s="23">
         <f>IFERROR(C49*SQRT(DATI_INPUT!$B$11/DATI_INPUT!$B$10)/(2*DATI_INPUT!$B$6),"")</f>
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="D68" s="36" t="s">
         <v>36</v>
@@ -20815,7 +20815,7 @@
         <f t="array" ref="C69">IF(ISNA(getqadim(C68)),
     "s fuori dal campo dell'abaco di portata (ammesso: "&amp;GetAbacoXRange("Q",0,0)&amp;")",
     IFERROR(getqadim(C68),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>1.4436900037729197</v>
+        <v>1.4245832020239257</v>
       </c>
       <c r="D69" s="36" t="s">
         <v>36</v>
@@ -20830,7 +20830,7 @@
       </c>
       <c r="C70" s="24">
         <f>IFERROR(C69*DATI_INPUT!$B$11*DATI_INPUT!$B$6*1000*3600,"")</f>
-        <v>1.5591852040747534E-2</v>
+        <v>1.8462598298230077</v>
       </c>
       <c r="D70" s="36" t="s">
         <v>77</v>
@@ -20845,7 +20845,7 @@
       </c>
       <c r="C71" s="24">
         <f>IFERROR(C70*DATI_INPUT!$B$33,"")</f>
-        <v>0.77959260203737668</v>
+        <v>92.312991491150385</v>
       </c>
       <c r="D71" s="36" t="s">
         <v>79</v>
@@ -20996,11 +20996,11 @@
       </c>
       <c r="G4" s="27">
         <f>ANALISI!C50</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H4" s="27" cm="1">
         <f t="array" ref="H4">GetEfficienza(B$2,I4,G4)</f>
-        <v>0.55947920568839982</v>
+        <v>0.59863853124999977</v>
       </c>
       <c r="I4" s="27">
         <v>0.5</v>
@@ -21023,11 +21023,11 @@
       </c>
       <c r="G5" s="28">
         <f>G4</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H5" s="28" cm="1">
         <f t="array" ref="H5">GetEfficienza(B$2,I5,G5)</f>
-        <v>0.45662622420999999</v>
+        <v>0.48746754375000001</v>
       </c>
       <c r="I5" s="28">
         <v>1</v>
@@ -21557,11 +21557,11 @@
       </c>
       <c r="J4" s="27">
         <f>ANALISI!C50</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="K4" s="27" cm="1">
         <f t="array" ref="K4">GetEfficienza(B$2,L4,J4)</f>
-        <v>0.66028974976300003</v>
+        <v>0.69622806937500004</v>
       </c>
       <c r="L4" s="27">
         <v>0.5</v>
@@ -21591,11 +21591,11 @@
       </c>
       <c r="J5" s="28">
         <f>J4</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="K5" s="28" cm="1">
         <f t="array" ref="K5">GetEfficienza(B$2,L5,J5)</f>
-        <v>0.5735879373399998</v>
+        <v>0.60360433249999978</v>
       </c>
       <c r="L5" s="28">
         <v>1</v>
@@ -21625,11 +21625,11 @@
       </c>
       <c r="J6" s="27">
         <f>J5</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="K6" s="27" cm="1">
         <f t="array" ref="K6">GetEfficienza(B$2,L6,J6)</f>
-        <v>0.38189168558999992</v>
+        <v>0.40197685124999999</v>
       </c>
       <c r="L6" s="27">
         <v>1.5</v>
@@ -22242,11 +22242,11 @@
       </c>
       <c r="M4" s="30">
         <f>ANALISI!C50</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N4" s="27" cm="1">
         <f t="array" ref="N4">GetEfficienza(B$2,O4,M4)</f>
-        <v>0.67051290760500026</v>
+        <v>0.70497948562500012</v>
       </c>
       <c r="O4" s="27">
         <v>0.5</v>
@@ -22283,11 +22283,11 @@
       </c>
       <c r="M5" s="28">
         <f>M4</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N5" s="28" cm="1">
         <f t="array" ref="N5">GetEfficienza(B$2,O5,M5)</f>
-        <v>0.58262154653999998</v>
+        <v>0.61116133249999993</v>
       </c>
       <c r="O5" s="28">
         <v>1</v>
@@ -22324,11 +22324,11 @@
       </c>
       <c r="M6" s="30">
         <f>M5</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N6" s="27" cm="1">
         <f t="array" ref="N6">GetEfficienza(B$2,O6,M6)</f>
-        <v>0.38744974940999988</v>
+        <v>0.40615135874999991</v>
       </c>
       <c r="O6" s="27">
         <v>1.5</v>
@@ -22365,11 +22365,11 @@
       </c>
       <c r="M7" s="28">
         <f>M5</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N7" s="28" cm="1">
         <f t="array" ref="N7">GetEfficienza(B$2,O7,M7)</f>
-        <v>0.29188622011999998</v>
+        <v>0.30604324999999999</v>
       </c>
       <c r="O7" s="28">
         <v>2</v>
@@ -23064,11 +23064,11 @@
       </c>
       <c r="M4" s="30">
         <f>ANALISI!C50</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N4" s="27" cm="1">
         <f t="array" ref="N4">GetEfficienza(B$2,O4,M4)</f>
-        <v>0.66112118264270003</v>
+        <v>0.69403893906250014</v>
       </c>
       <c r="O4" s="27">
         <v>0.5</v>
@@ -23105,11 +23105,11 @@
       </c>
       <c r="M5" s="28">
         <f>M4</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N5" s="28" cm="1">
         <f t="array" ref="N5">GetEfficienza(B$2,O5,M5)</f>
-        <v>0.58040621819999993</v>
+        <v>0.60852397999999996</v>
       </c>
       <c r="O5" s="28">
         <v>1</v>
@@ -23146,11 +23146,11 @@
       </c>
       <c r="M6" s="30">
         <f>M5</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N6" s="27" cm="1">
         <f t="array" ref="N6">GetEfficienza(B$2,O6,M6)</f>
-        <v>0.38757742711999998</v>
+        <v>0.406518555</v>
       </c>
       <c r="O6" s="27">
         <v>1.5</v>
@@ -23187,11 +23187,11 @@
       </c>
       <c r="M7" s="28">
         <f>M5</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="N7" s="28" cm="1">
         <f t="array" ref="N7">GetEfficienza(B$2,O7,M7)</f>
-        <v>0.29061003300999994</v>
+        <v>0.30491350874999995</v>
       </c>
       <c r="O7" s="28">
         <v>2</v>
@@ -23928,11 +23928,11 @@
       </c>
       <c r="G4" s="27">
         <f>ANALISI!C50</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H4" s="27" cm="1">
         <f t="array" ref="H4">gett("T50",E$2,I$4,G4)</f>
-        <v>5.6070799662189405E-2</v>
+        <v>5.3837298147770163E-2</v>
       </c>
       <c r="I4" s="27">
         <v>0.5</v>
@@ -23955,11 +23955,11 @@
       </c>
       <c r="G5" s="28">
         <f>G4</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H5" s="28" cm="1">
         <f t="array" ref="H5">gett("T50",E$2,I$5,G5)</f>
-        <v>7.9200150582331291E-2</v>
+        <v>7.6393315101689729E-2</v>
       </c>
       <c r="I5" s="28">
         <v>1</v>
@@ -24473,11 +24473,11 @@
       </c>
       <c r="G4" s="27">
         <f>ANALISI!C50</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H4" s="27" cm="1">
         <f t="array" ref="H4">gett("T90",E$2,I$4,G4)</f>
-        <v>0.47036771234865554</v>
+        <v>0.44054769468300675</v>
       </c>
       <c r="I4" s="27">
         <v>0.5</v>
@@ -24500,11 +24500,11 @@
       </c>
       <c r="G5" s="28">
         <f>G4</f>
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H5" s="28" cm="1">
         <f t="array" ref="H5">gett("T90",E$2,I$5,G5)</f>
-        <v>0.51229916295151534</v>
+        <v>0.48537651044101932</v>
       </c>
       <c r="I5" s="28">
         <v>1</v>

--- a/articolo_06_trincee-drenanti-foglio/Trincee_Drenanti_v1_0.xlsx
+++ b/articolo_06_trincee-drenanti-foglio/Trincee_Drenanti_v1_0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\_Francisco\_GitHub\franciscojmendez_Risorse\articolo_06_trincee-drenanti-foglio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF985399-A5D0-4678-B8ED-B0C9D548A8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFC41C7F-C839-499C-9667-33EFC263F3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3C2956EA-F146-457E-A9D7-5BDD1E22F3AE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{3C2956EA-F146-457E-A9D7-5BDD1E22F3AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Credits" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="Abaco_Portata" sheetId="7" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">ANALISI!$B$1:$G$71</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">ANALISI!$B$1:$G$73</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Credits!$B$2:$B$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">DATI_INPUT!$A$1:$D$33</definedName>
     <definedName name="beta">DATI_INPUT!$B$7</definedName>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="136">
   <si>
     <t>Trincee Drenanti - Dimensionamento di Massima</t>
   </si>
@@ -412,9 +412,6 @@
     <t>S/H0 di progetto = S / H0</t>
   </si>
   <si>
-    <t>E ottenuta = GetEfficienza(n, d, S/H0 di progetto)</t>
-  </si>
-  <si>
     <t>Verifica</t>
   </si>
   <si>
@@ -422,12 +419,6 @@
   </si>
   <si>
     <t>Interasse di progetto (valore medio rappresentativo &lt;= valore teorico):</t>
-  </si>
-  <si>
-    <t>T50 = GetT("T50", n, d, S/H0 di progetto)</t>
-  </si>
-  <si>
-    <t>T90 = GetT("T90", n, d, S/H0 di progetto)</t>
   </si>
   <si>
     <t>Delta F ottenuto = E ottenuta * Delta Fmax</t>
@@ -440,12 +431,6 @@
   </si>
   <si>
     <t>F a t90  = F0 + 0.9 * Delta F ottenuto</t>
-  </si>
-  <si>
-    <t>S/H0 teorico = GetSuH0(n, d, E richiesta)</t>
-  </si>
-  <si>
-    <t>S teorico = (S/H0 suggerito) * H0</t>
   </si>
   <si>
     <t xml:space="preserve">n </t>
@@ -494,6 +479,30 @@
   </si>
   <si>
     <t xml:space="preserve">n per calcolo tempi  -&gt;  n_t   </t>
+  </si>
+  <si>
+    <t>S*/H0 teorico = GetSuH0(n, d, E richiesta)</t>
+  </si>
+  <si>
+    <t>S* teorico= S*/H0 teorico × H0</t>
+  </si>
+  <si>
+    <t>S teorico = S* teorico × √(kh/kv)</t>
+  </si>
+  <si>
+    <t>E ottenuta = GetEfficienza(n, d, S*/H0 di progetto)</t>
+  </si>
+  <si>
+    <t>T50 = GetT("T50", n, d, S*/H0 di progetto)</t>
+  </si>
+  <si>
+    <t>T90 = GetT("T90", n, d, S*/H0 di progetto)</t>
+  </si>
+  <si>
+    <t>S*/H0</t>
+  </si>
+  <si>
+    <t>S* di progetto =  S / H0 × √(kv/kh)</t>
   </si>
 </sst>
 </file>
@@ -772,7 +781,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -835,9 +844,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -859,6 +865,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -870,16 +901,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2167,7 +2188,7 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1.25</c:v>
+                  <c:v>1.4142135623730951</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2179,7 +2200,7 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1.4245832020239257</c:v>
+                  <c:v>1.4529920652750568</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3002,13 +3023,13 @@
             <c:numRef>
               <c:f>Abaco_Efficienza_n1!$G$4:$G$5</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                <c:pt idx="0">
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3020,10 +3041,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.59863853124999977</c:v>
+                  <c:v>0.53640635954570071</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.48746754375000001</c:v>
+                  <c:v>0.43807348232928089</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3994,16 +4015,16 @@
             <c:numRef>
               <c:f>'Abaco_Efficienza_n1,5'!$J$4:$J$6</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="3"/>
-                <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                <c:pt idx="0">
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
-                </c:pt>
-                <c:pt idx="2" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4015,13 +4036,13 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.69622806937500004</c:v>
+                  <c:v>0.63793686004157357</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.60360433249999978</c:v>
+                  <c:v>0.55499293199886912</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>0.40197685124999999</c:v>
+                  <c:v>0.36945748366701492</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5137,19 +5158,19 @@
             <c:numRef>
               <c:f>'Abaco_Efficienza_n2,5'!$M$4:$M$7</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5161,16 +5182,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.70497948562500012</c:v>
+                  <c:v>0.64918452669368176</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.61116133249999993</c:v>
+                  <c:v>0.56502372001094692</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>0.40615135874999991</c:v>
+                  <c:v>0.37593982270042831</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30604324999999999</c:v>
+                  <c:v>0.28315113907235595</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6365,19 +6386,19 @@
             <c:numRef>
               <c:f>Abaco_Efficienza_n4!$M$4:$M$7</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6389,16 +6410,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.69403893906250014</c:v>
+                  <c:v>0.64122391789387723</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.60852397999999996</c:v>
+                  <c:v>0.56308025213927571</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>0.406518555</c:v>
+                  <c:v>0.37590754473629984</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30491350874999995</c:v>
+                  <c:v>0.28178203807144114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7236,13 +7257,13 @@
             <c:numRef>
               <c:f>'Abaco_Tempi_T50-n1'!$G$4:$G$5</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="2"/>
-                <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                <c:pt idx="0">
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7254,10 +7275,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>5.3837298147770163E-2</c:v>
+                  <c:v>5.7036767641874646E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.6393315101689729E-2</c:v>
+                  <c:v>8.0309867313937494E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8138,10 +8159,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8153,10 +8174,10 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.44054769468300675</c:v>
+                  <c:v>0.48711498953969745</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.48537651044101932</c:v>
+                  <c:v>0.52593193263720761</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9360,19 +9381,19 @@
             <c:numRef>
               <c:f>'Abaco_Tempi_T50-n2,5'!$M$4:$M$7</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="4"/>
-                <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                <c:pt idx="0">
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
-                </c:pt>
-                <c:pt idx="2" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9384,16 +9405,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>0.12505250388889821</c:v>
+                  <c:v>0.14329877055356044</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.18846199981652903</c:v>
+                  <c:v>0.22109748867241455</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>0.9350477335751991</c:v>
+                  <c:v>1.0010195080760327</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4629907179962951</c:v>
+                  <c:v>1.5296888446312651</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10638,19 +10659,19 @@
             <c:numRef>
               <c:f>'Abaco_Tempi_T90-n2,5'!$M$4:$M$7</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="4"/>
-                <c:pt idx="0" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                <c:pt idx="0">
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
-                </c:pt>
-                <c:pt idx="2" formatCode="0.000">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5</c:v>
+                  <c:v>2.8284271247461903</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10662,16 +10683,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0" formatCode="0.000">
-                  <c:v>1.9201112403645975</c:v>
+                  <c:v>2.3104516086273907</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.6546631211364748</c:v>
+                  <c:v>2.9288989432352714</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
-                  <c:v>3.8684792970592765</c:v>
+                  <c:v>4.0830656230461484</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.3971406149947496</c:v>
+                  <c:v>4.6028108630895197</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17200,6 +17221,28 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="459" row="6">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{380CF535-67C0-4866-857C-5CCD76E838A0}">
+  <we:reference id="wa200010725" version="1.0.0.1" store="it-IT" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010725" version="1.0.0.1" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;8d5de819-6bd7-4788-ae57-53d62d7cf778&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Foglio1">
@@ -17262,7 +17305,7 @@
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B15" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
@@ -17322,7 +17365,7 @@
     </row>
     <row r="29" spans="2:2" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B29" s="19" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.2">
@@ -17333,9 +17376,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B33" s="19" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.2">
@@ -17351,7 +17394,7 @@
     </row>
     <row r="38" spans="2:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B38" s="19" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -17359,7 +17402,7 @@
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B40" s="19" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="2:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17400,20 +17443,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Y1" s="3"/>
@@ -17435,33 +17478,33 @@
     </row>
     <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B2">
         <v>2.5</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E2">
         <v>2.5</v>
       </c>
       <c r="G2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H2">
         <v>2.5</v>
       </c>
       <c r="J2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="K2">
         <v>2.5</v>
       </c>
-      <c r="M2" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="N2" s="45"/>
+      <c r="M2" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="N2" s="41"/>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -17489,7 +17532,7 @@
         <v>2</v>
       </c>
       <c r="M3" s="26" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="N3" s="26" t="s">
         <v>96</v>
@@ -17500,38 +17543,38 @@
     </row>
     <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>81</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>81</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H4" s="15" t="s">
         <v>81</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="M4" s="27">
-        <f>ANALISI!C50</f>
-        <v>2.5</v>
+      <c r="M4" s="38">
+        <f>ANALISI!C52</f>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N4" s="27" cm="1">
         <f t="array" ref="N4">gett("T50",E$2,O$4,M4)</f>
-        <v>0.12505250388889821</v>
+        <v>0.14329877055356044</v>
       </c>
       <c r="O4" s="27">
         <v>0.5</v>
@@ -17566,13 +17609,13 @@
         <f t="array" ref="K5">gett("T50",K$2,K$3,J5)</f>
         <v>0.88201604018118962</v>
       </c>
-      <c r="M5" s="28">
+      <c r="M5" s="39">
         <f>M4</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N5" s="28" cm="1">
         <f t="array" ref="N5">gett("T50",E$2,O$5,M5)</f>
-        <v>0.18846199981652903</v>
+        <v>0.22109748867241455</v>
       </c>
       <c r="O5" s="28">
         <v>1</v>
@@ -17607,13 +17650,13 @@
         <f t="array" ref="K6">gett("T50",K$2,K$3,J6)</f>
         <v>0.93693255230490624</v>
       </c>
-      <c r="M6" s="27">
+      <c r="M6" s="38">
         <f>M5</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N6" s="27" cm="1">
         <f t="array" ref="N6">gett("T50",E$2,O$6,M6)</f>
-        <v>0.9350477335751991</v>
+        <v>1.0010195080760327</v>
       </c>
       <c r="O6" s="27">
         <v>1.5</v>
@@ -17648,13 +17691,13 @@
         <f t="array" ref="K7">gett("T50",K$2,K$3,J7)</f>
         <v>1.018478290239208</v>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="39">
         <f>M6</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N7" s="28" cm="1">
         <f t="array" ref="N7">gett("T50",E$2,O$7,M7)</f>
-        <v>1.4629907179962951</v>
+        <v>1.5296888446312651</v>
       </c>
       <c r="O7" s="28">
         <v>2</v>
@@ -18311,20 +18354,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Y1" s="3"/>
@@ -18346,33 +18389,33 @@
     </row>
     <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B2">
         <v>2.5</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E2">
         <v>2.5</v>
       </c>
       <c r="G2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H2">
         <v>2.5</v>
       </c>
       <c r="J2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="K2">
         <v>2.5</v>
       </c>
-      <c r="M2" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="N2" s="45"/>
+      <c r="M2" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="N2" s="41"/>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -18400,7 +18443,7 @@
         <v>2</v>
       </c>
       <c r="M3" s="26" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="N3" s="26" t="s">
         <v>96</v>
@@ -18411,38 +18454,38 @@
     </row>
     <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>81</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>81</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H4" s="15" t="s">
         <v>81</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>81</v>
       </c>
       <c r="M4" s="27">
-        <f>ANALISI!C50</f>
-        <v>2.5</v>
+        <f>ANALISI!C52</f>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N4" s="27" cm="1">
         <f t="array" ref="N4">gett("T90",E$2,O$4,M4)</f>
-        <v>1.9201112403645975</v>
+        <v>2.3104516086273907</v>
       </c>
       <c r="O4" s="27">
         <v>0.5</v>
@@ -18477,13 +18520,13 @@
         <f t="array" ref="K5">gett("T90",K$2,K$3,J5)</f>
         <v>2.7673687278347439</v>
       </c>
-      <c r="M5" s="28">
+      <c r="M5" s="37">
         <f>M4</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N5" s="28" cm="1">
         <f t="array" ref="N5">gett("T90",E$2,O$5,M5)</f>
-        <v>2.6546631211364748</v>
+        <v>2.9288989432352714</v>
       </c>
       <c r="O5" s="28">
         <v>1</v>
@@ -18520,11 +18563,11 @@
       </c>
       <c r="M6" s="27">
         <f>M5</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N6" s="27" cm="1">
         <f t="array" ref="N6">gett("T90",E$2,O$6,M6)</f>
-        <v>3.8684792970592765</v>
+        <v>4.0830656230461484</v>
       </c>
       <c r="O6" s="27">
         <v>1.5</v>
@@ -18559,13 +18602,13 @@
         <f t="array" ref="K7">gett("T90",K$2,K$3,J7)</f>
         <v>3.0512167429087724</v>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="37">
         <f>M6</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N7" s="28" cm="1">
         <f t="array" ref="N7">gett("T90",E$2,O$7,M7)</f>
-        <v>4.3971406149947496</v>
+        <v>4.6028108630895197</v>
       </c>
       <c r="O7" s="28">
         <v>2</v>
@@ -19264,12 +19307,12 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19278,10 +19321,10 @@
       <c r="B3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="45"/>
+      <c r="E3" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="41"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -19307,12 +19350,12 @@
         <v>8.8217326810333924E-2</v>
       </c>
       <c r="E5" s="27">
-        <f>ANALISI!C68</f>
-        <v>1.25</v>
+        <f>ANALISI!C70</f>
+        <v>1.4142135623730951</v>
       </c>
       <c r="F5" s="27">
         <f>IFERROR(getqadim(E5),"")</f>
-        <v>1.4245832020239257</v>
+        <v>1.4529920652750568</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -19591,8 +19634,8 @@
       <c r="A10" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="35">
-        <v>5.9999999999999995E-8</v>
+      <c r="B10" s="34">
+        <v>6E-9</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>31</v>
@@ -19604,8 +19647,8 @@
       <c r="A11" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="35">
-        <v>5.9999999999999995E-8</v>
+      <c r="B11" s="34">
+        <v>3E-9</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>31</v>
@@ -19747,7 +19790,7 @@
       <c r="A23" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="31">
         <v>1.3</v>
       </c>
       <c r="C23" s="15" t="s">
@@ -19758,9 +19801,9 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B24" s="32">
+        <v>117</v>
+      </c>
+      <c r="B24" s="31">
         <v>1.1000000000000001</v>
       </c>
       <c r="C24" s="15" t="s">
@@ -19780,7 +19823,7 @@
         <v>45</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E25" s="12"/>
     </row>
@@ -19811,7 +19854,7 @@
         <v>36</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E28" s="12"/>
     </row>
@@ -19831,8 +19874,8 @@
       <c r="E29" s="12"/>
     </row>
     <row r="30" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="34" t="s">
-        <v>132</v>
+      <c r="A30" s="33" t="s">
+        <v>127</v>
       </c>
       <c r="B30" s="21">
         <v>2.5</v>
@@ -19840,8 +19883,8 @@
       <c r="C30" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="33" t="s">
-        <v>130</v>
+      <c r="D30" s="32" t="s">
+        <v>125</v>
       </c>
       <c r="E30" s="12"/>
     </row>
@@ -19932,12 +19975,12 @@
   <sheetPr codeName="Foglio3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:Q71"/>
+  <dimension ref="B1:Q73"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="66.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.140625" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -19948,27 +19991,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="P2" s="2"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
       <c r="Q3" s="4"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
@@ -20363,14 +20406,14 @@
       <c r="M25" s="4"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
@@ -20380,12 +20423,12 @@
         <f>DATI_INPUT!$B$23</f>
         <v>1.3</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
@@ -20395,12 +20438,12 @@
         <f>mesi_target</f>
         <v>6</v>
       </c>
-      <c r="D30" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
+      <c r="D30" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
@@ -20410,22 +20453,22 @@
         <f>"F ≥ "&amp;F_short&amp;" raggiunto entro "&amp;DATI_INPUT!$B$25&amp;" mesi "</f>
         <v xml:space="preserve">F ≥ 1,1 raggiunto entro 6 mesi </v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="37"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="40"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
@@ -20435,12 +20478,12 @@
         <f>IFERROR(GetFZ(D_piano,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
         <v>0.95706292485134314</v>
       </c>
-      <c r="D35" s="36" t="s">
+      <c r="D35" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
@@ -20450,12 +20493,12 @@
         <f>IFERROR(GetFZ(D_piano,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
         <v>1.5937531595749261</v>
       </c>
-      <c r="D36" s="36" t="s">
+      <c r="D36" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
@@ -20465,12 +20508,12 @@
         <f>C29-C35</f>
         <v>0.3429370751486569</v>
       </c>
-      <c r="D37" s="36" t="s">
+      <c r="D37" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
@@ -20480,12 +20523,12 @@
         <f>C36-C35</f>
         <v>0.63669023472358299</v>
       </c>
-      <c r="D38" s="36" t="s">
+      <c r="D38" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="37"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
@@ -20495,22 +20538,22 @@
         <f>C37/C38</f>
         <v>0.53862468190287527</v>
       </c>
-      <c r="D39" s="36" t="s">
+      <c r="D39" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B41" s="40" t="s">
+      <c r="B41" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="40"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
@@ -20520,22 +20563,22 @@
         <f>DATI_INPUT!$B$28&amp;" / "&amp;DATI_INPUT!$B$29</f>
         <v>1,5 / 1</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="D43" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="37"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="45"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="C44" s="37"/>
+      <c r="B44" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="C44" s="45"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C45" s="7" cm="1">
         <f t="array" ref="C45">IF(ISNA(getsuh0(n_cfg,d_cfg,C39)),
@@ -20543,316 +20586,344 @@
     IFERROR(getsuh0(n_cfg,d_cfg,C39),"-&gt; importa ModuloTrincee.bas"))</f>
         <v>2.9446791221275923</v>
       </c>
-      <c r="D45" s="36" t="s">
+      <c r="D45" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
-    </row>
-    <row r="46" spans="2:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E45" s="45"/>
+      <c r="F45" s="45"/>
+      <c r="G45" s="45"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C46" s="31">
+        <v>129</v>
+      </c>
+      <c r="C46" s="30">
         <f>IF(ISNUMBER(C45),C45*H0,C45)</f>
         <v>17.668074732765554</v>
       </c>
-      <c r="D46" s="36" t="s">
+      <c r="D46" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="37"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
+      <c r="B47" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" s="30">
+        <f>C46*SQRT(kh/kv)</f>
+        <v>24.986430908098445</v>
+      </c>
+      <c r="D47" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C48" s="37"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C49" s="9">
-        <v>15</v>
-      </c>
-      <c r="D49" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="37"/>
+      <c r="B49" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" s="45"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C50" s="6">
-        <f>IFERROR(C49/H0,"")</f>
-        <v>2.5</v>
-      </c>
-      <c r="D50" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
+        <v>103</v>
+      </c>
+      <c r="C50" s="9">
+        <v>24</v>
+      </c>
+      <c r="D50" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C51" s="7" cm="1">
-        <f t="array" ref="C51">IF(ISNA(GetEfficienza(n_cfg,d_cfg,C50)),
-    "S/H0 di progetto fuori dal campo dell'abaco (S/H0 ammesso: "&amp;GetAbacoXRange("EFF",n_cfg,d_cfg)&amp;")",
-    IFERROR(GetEfficienza(n_cfg,d_cfg,C50),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>0.60360433249999978</v>
-      </c>
-      <c r="D51" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="C51" s="23">
+        <f>IFERROR(C50/H0,"")</f>
+        <v>4</v>
+      </c>
+      <c r="D51" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="37"/>
+      <c r="E51" s="45"/>
+      <c r="F51" s="45"/>
+      <c r="G51" s="45"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C52" s="7" t="str">
-        <f>IF(OR(NOT(ISNUMBER(C51)),NOT(ISNUMBER(C39))),"-&gt; importa ModuloTrincee.bas",IF(C51&gt;=C39,"VERIFICATO: interasse scelto soddisfa F_target","NON VERIFICATO: ridurre interasse o rivedere F_target"))</f>
+        <v>135</v>
+      </c>
+      <c r="C52" s="23">
+        <f>C51*SQRT(kv/kh)</f>
+        <v>2.8284271247461903</v>
+      </c>
+      <c r="D52" s="35"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="36"/>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" s="7" cm="1">
+        <f t="array" ref="C53">IF(ISNA(GetEfficienza(n_cfg,d_cfg,C52)),
+    "S/H0 di progetto fuori dal campo dell'abaco (S/H0 ammesso: "&amp;GetAbacoXRange("EFF",n_cfg,d_cfg)&amp;")",
+    IFERROR(GetEfficienza(n_cfg,d_cfg,C52),"-&gt; importa ModuloTrincee.bas"))</f>
+        <v>0.55499293199886912</v>
+      </c>
+      <c r="D53" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E53" s="45"/>
+      <c r="F53" s="45"/>
+      <c r="G53" s="45"/>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B54" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C54" s="7" t="str">
+        <f>IF(OR(NOT(ISNUMBER(C53)),NOT(ISNUMBER(C39))),"-&gt; importa ModuloTrincee.bas",IF(C53&gt;=C39,"VERIFICATO: interasse scelto soddisfa F_target","NON VERIFICATO: ridurre interasse o rivedere F_target"))</f>
         <v>VERIFICATO: interasse scelto soddisfa F_target</v>
       </c>
-      <c r="D52" s="38"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-      <c r="G52" s="39"/>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54" s="40" t="s">
+      <c r="D54" s="46"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="47"/>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="C54" s="40"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="40"/>
-      <c r="F54" s="40"/>
-      <c r="G54" s="40"/>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B56" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C56" s="7" cm="1">
-        <f t="array" ref="C56">IF(ISNA(gett("T50",n_tempi,d_cfg,C50)),
-    "S/H0 fuori dal campo dell'abaco T50 (ammesso: "&amp;GetAbacoXRange("T50",n_tempi,d_cfg)&amp;")",
-    IFERROR(gett("T50",n_tempi,d_cfg,C50),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>0.18846199981652903</v>
-      </c>
-      <c r="D56" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C57" s="7" cm="1">
-        <f t="array" ref="C57">IF(ISNA(gett("T90",n_tempi,d_cfg,C50)),
-    "S/H0 fuori dal campo dell'abaco T90 (ammesso: "&amp;GetAbacoXRange("T90",n_tempi,d_cfg)&amp;")",
-    IFERROR(gett("T90",n_tempi,d_cfg,C50),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>2.6546631211364748</v>
-      </c>
-      <c r="D57" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="48"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C58" s="23">
-        <f>IFERROR(C56*(2*(1+nu)*(1-2*nu)*gammaw*H0^2)/(Emod*kv)/(30*86400),"")</f>
-        <v>0.21398289562501735</v>
-      </c>
-      <c r="D58" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
+        <v>132</v>
+      </c>
+      <c r="C58" s="7" cm="1">
+        <f t="array" ref="C58">IF(ISNA(gett("T50",n_tempi,d_cfg,C52)),
+    "S/H0 fuori dal campo dell'abaco T50 (ammesso: "&amp;GetAbacoXRange("T50",n_tempi,d_cfg)&amp;")",
+    IFERROR(gett("T50",n_tempi,d_cfg,C52),"-&gt; importa ModuloTrincee.bas"))</f>
+        <v>0.22109748867241455</v>
+      </c>
+      <c r="D58" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E58" s="45"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="45"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C59" s="23">
-        <f>IFERROR(C57*(2*(1+nu)*(1-2*nu)*gammaw*H0^2)/(Emod*kv)/(30*86400),"")</f>
-        <v>3.0141487521237069</v>
-      </c>
-      <c r="D59" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
+        <v>133</v>
+      </c>
+      <c r="C59" s="7" cm="1">
+        <f t="array" ref="C59">IF(ISNA(gett("T90",n_tempi,d_cfg,C52)),
+    "S/H0 fuori dal campo dell'abaco T90 (ammesso: "&amp;GetAbacoXRange("T90",n_tempi,d_cfg)&amp;")",
+    IFERROR(gett("T90",n_tempi,d_cfg,C52),"-&gt; importa ModuloTrincee.bas"))</f>
+        <v>2.9288989432352714</v>
+      </c>
+      <c r="D59" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E59" s="45"/>
+      <c r="F59" s="45"/>
+      <c r="G59" s="45"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C60" s="8">
-        <f>IFERROR(C51*C38,"")</f>
-        <v>0.38430898413959652</v>
-      </c>
-      <c r="D60" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="37"/>
+        <v>71</v>
+      </c>
+      <c r="C60" s="23">
+        <f>IFERROR(C58*(2*(1+nu)*(1-2*nu)*gammaw*H0^2)/(Emod*kv)/(30*86400),"")</f>
+        <v>5.0207554719360807</v>
+      </c>
+      <c r="D60" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="E60" s="45"/>
+      <c r="F60" s="45"/>
+      <c r="G60" s="45"/>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C61" s="7">
-        <f>IFERROR(C35+C60,"")</f>
-        <v>1.3413719089909397</v>
-      </c>
-      <c r="D61" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="37"/>
+        <v>72</v>
+      </c>
+      <c r="C61" s="23">
+        <f>IFERROR(C59*(2*(1+nu)*(1-2*nu)*gammaw*H0^2)/(Emod*kv)/(30*86400),"")</f>
+        <v>66.510413502634279</v>
+      </c>
+      <c r="D61" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" s="45"/>
+      <c r="F61" s="45"/>
+      <c r="G61" s="45"/>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C62" s="8">
-        <f>IFERROR(C35+0.5*C60,"")</f>
-        <v>1.1492174169211413</v>
-      </c>
-      <c r="D62" s="36" t="s">
+        <f>IFERROR(C53*C38,"")</f>
+        <v>0.3533585801442895</v>
+      </c>
+      <c r="D62" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="37"/>
+      <c r="E62" s="45"/>
+      <c r="F62" s="45"/>
+      <c r="G62" s="45"/>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C63" s="8">
-        <f>IFERROR(C35+0.9*C60,"")</f>
-        <v>1.3029410105769801</v>
-      </c>
-      <c r="D63" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" s="7">
+        <f>IFERROR(C35+C62,"")</f>
+        <v>1.3104215049956327</v>
+      </c>
+      <c r="D63" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="37"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="45"/>
+      <c r="G63" s="45"/>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C64" s="7" t="str">
-        <f>IF(AND(C62 &gt;= F_short, C58 &lt;= mesi_target), "VERIFICATO", "NON verificato")</f>
+        <v>110</v>
+      </c>
+      <c r="C64" s="8">
+        <f>IFERROR(C35+0.5*C62,"")</f>
+        <v>1.1337422149234879</v>
+      </c>
+      <c r="D64" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E64" s="45"/>
+      <c r="F64" s="45"/>
+      <c r="G64" s="45"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C65" s="8">
+        <f>IFERROR(C35+0.9*C62,"")</f>
+        <v>1.2750856469812037</v>
+      </c>
+      <c r="D65" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E65" s="45"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C66" s="7" t="str">
+        <f>IF(AND(C64 &gt;= F_short, C60 &lt;= mesi_target), "VERIFICATO", "NON verificato")</f>
         <v>VERIFICATO</v>
       </c>
-      <c r="D64" s="3"/>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B66" s="40" t="s">
+      <c r="D66" s="3"/>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="C66" s="40"/>
-      <c r="D66" s="40"/>
-      <c r="E66" s="40"/>
-      <c r="F66" s="40"/>
-      <c r="G66" s="40"/>
-    </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B68" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C68" s="23">
-        <f>IFERROR(C49*SQRT(DATI_INPUT!$B$11/DATI_INPUT!$B$10)/(2*DATI_INPUT!$B$6),"")</f>
-        <v>1.25</v>
-      </c>
-      <c r="D68" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="37"/>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B69" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C69" s="23" cm="1">
-        <f t="array" ref="C69">IF(ISNA(getqadim(C68)),
-    "s fuori dal campo dell'abaco di portata (ammesso: "&amp;GetAbacoXRange("Q",0,0)&amp;")",
-    IFERROR(getqadim(C68),"-&gt; importa ModuloTrincee.bas"))</f>
-        <v>1.4245832020239257</v>
-      </c>
-      <c r="D69" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="37"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="48"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="48"/>
+      <c r="G68" s="48"/>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C70" s="24">
-        <f>IFERROR(C69*DATI_INPUT!$B$11*DATI_INPUT!$B$6*1000*3600,"")</f>
-        <v>1.8462598298230077</v>
-      </c>
-      <c r="D70" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="37"/>
+        <v>74</v>
+      </c>
+      <c r="C70" s="23">
+        <f>IFERROR(C50*SQRT(DATI_INPUT!$B$11/DATI_INPUT!$B$10)/(2*DATI_INPUT!$B$6),"")</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="D70" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E70" s="45"/>
+      <c r="F70" s="45"/>
+      <c r="G70" s="45"/>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" s="23" cm="1">
+        <f t="array" ref="C71">IF(ISNA(getqadim(C70)),
+    "s fuori dal campo dell'abaco di portata (ammesso: "&amp;GetAbacoXRange("Q",0,0)&amp;")",
+    IFERROR(getqadim(C70),"-&gt; importa ModuloTrincee.bas"))</f>
+        <v>1.4529920652750568</v>
+      </c>
+      <c r="D71" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E71" s="45"/>
+      <c r="F71" s="45"/>
+      <c r="G71" s="45"/>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B72" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C72" s="24">
+        <f>IFERROR(C71*DATI_INPUT!$B$11*DATI_INPUT!$B$6*1000*3600,"")</f>
+        <v>9.4153885829823675E-2</v>
+      </c>
+      <c r="D72" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="E72" s="45"/>
+      <c r="F72" s="45"/>
+      <c r="G72" s="45"/>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B73" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C71" s="24">
-        <f>IFERROR(C70*DATI_INPUT!$B$33,"")</f>
-        <v>92.312991491150385</v>
-      </c>
-      <c r="D71" s="36" t="s">
+      <c r="C73" s="24">
+        <f>IFERROR(C72*DATI_INPUT!$B$33,"")</f>
+        <v>4.7076942914911841</v>
+      </c>
+      <c r="D73" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="E71" s="37"/>
-      <c r="F71" s="37"/>
-      <c r="G71" s="37"/>
+      <c r="E73" s="45"/>
+      <c r="F73" s="45"/>
+      <c r="G73" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -20869,29 +20940,29 @@
     <mergeCell ref="D36:G36"/>
     <mergeCell ref="D37:G37"/>
     <mergeCell ref="D30:G30"/>
-    <mergeCell ref="D69:G69"/>
-    <mergeCell ref="D70:G70"/>
     <mergeCell ref="D71:G71"/>
+    <mergeCell ref="D72:G72"/>
+    <mergeCell ref="D73:G73"/>
+    <mergeCell ref="D63:G63"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B68:G68"/>
+    <mergeCell ref="D62:G62"/>
     <mergeCell ref="D61:G61"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B66:G66"/>
     <mergeCell ref="D60:G60"/>
     <mergeCell ref="D59:G59"/>
     <mergeCell ref="D58:G58"/>
-    <mergeCell ref="D57:G57"/>
-    <mergeCell ref="D56:G56"/>
-    <mergeCell ref="D68:G68"/>
-    <mergeCell ref="D62:G62"/>
-    <mergeCell ref="D63:G63"/>
-    <mergeCell ref="D51:G51"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D70:G70"/>
+    <mergeCell ref="D64:G64"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="D53:G53"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="B49:C49"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="D43:G43"/>
     <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D46:G46"/>
-    <mergeCell ref="D49:G49"/>
+    <mergeCell ref="D47:G47"/>
     <mergeCell ref="D50:G50"/>
+    <mergeCell ref="D51:G51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -20913,14 +20984,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="S1" s="3"/>
@@ -20942,21 +21013,21 @@
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="G2" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="45"/>
+      <c r="G2" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="H2" s="41"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -20972,7 +21043,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="H3" s="26" t="s">
         <v>96</v>
@@ -20983,10 +21054,10 @@
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>85</v>
@@ -20995,12 +21066,12 @@
         <v>86</v>
       </c>
       <c r="G4" s="27">
-        <f>ANALISI!C50</f>
-        <v>2.5</v>
+        <f>ANALISI!C52</f>
+        <v>2.8284271247461903</v>
       </c>
       <c r="H4" s="27" cm="1">
         <f t="array" ref="H4">GetEfficienza(B$2,I4,G4)</f>
-        <v>0.59863853124999977</v>
+        <v>0.53640635954570071</v>
       </c>
       <c r="I4" s="27">
         <v>0.5</v>
@@ -21021,13 +21092,13 @@
         <f t="array" ref="E5">GetEfficienza(E$2,E$3,D5)</f>
         <v>0.81994611200393552</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="37">
         <f>G4</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="H5" s="28" cm="1">
         <f t="array" ref="H5">GetEfficienza(B$2,I5,G5)</f>
-        <v>0.48746754375000001</v>
+        <v>0.43807348232928089</v>
       </c>
       <c r="I5" s="28">
         <v>1</v>
@@ -21452,17 +21523,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="V1" s="3"/>
@@ -21484,27 +21555,27 @@
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B2">
         <v>1.5</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E2">
         <v>1.5</v>
       </c>
       <c r="G2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H2">
         <v>1.5</v>
       </c>
-      <c r="J2" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="K2" s="45"/>
+      <c r="J2" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="K2" s="41"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -21526,7 +21597,7 @@
         <v>1.5</v>
       </c>
       <c r="J3" s="26" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="K3" s="26" t="s">
         <v>96</v>
@@ -21537,10 +21608,10 @@
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>85</v>
@@ -21556,12 +21627,12 @@
         <v>86</v>
       </c>
       <c r="J4" s="27">
-        <f>ANALISI!C50</f>
-        <v>2.5</v>
+        <f>ANALISI!C52</f>
+        <v>2.8284271247461903</v>
       </c>
       <c r="K4" s="27" cm="1">
         <f t="array" ref="K4">GetEfficienza(B$2,L4,J4)</f>
-        <v>0.69622806937500004</v>
+        <v>0.63793686004157357</v>
       </c>
       <c r="L4" s="27">
         <v>0.5</v>
@@ -21589,13 +21660,13 @@
         <f t="array" ref="H5">GetEfficienza(H$2,H$3,G5)</f>
         <v>0.64772029102682993</v>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="37">
         <f>J4</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="K5" s="28" cm="1">
         <f t="array" ref="K5">GetEfficienza(B$2,L5,J5)</f>
-        <v>0.60360433249999978</v>
+        <v>0.55499293199886912</v>
       </c>
       <c r="L5" s="28">
         <v>1</v>
@@ -21625,11 +21696,11 @@
       </c>
       <c r="J6" s="27">
         <f>J5</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="K6" s="27" cm="1">
         <f t="array" ref="K6">GetEfficienza(B$2,L6,J6)</f>
-        <v>0.40197685124999999</v>
+        <v>0.36945748366701492</v>
       </c>
       <c r="L6" s="27">
         <v>1.5</v>
@@ -22115,20 +22186,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Y1" s="3"/>
@@ -22150,33 +22221,33 @@
     </row>
     <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B2">
         <v>2.5</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E2">
         <v>2.5</v>
       </c>
       <c r="G2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H2">
         <v>2.5</v>
       </c>
       <c r="J2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="K2">
         <v>2.5</v>
       </c>
-      <c r="M2" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="N2" s="45"/>
+      <c r="M2" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="N2" s="41"/>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -22204,7 +22275,7 @@
         <v>2</v>
       </c>
       <c r="M3" s="26" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="N3" s="26" t="s">
         <v>96</v>
@@ -22215,10 +22286,10 @@
     </row>
     <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>85</v>
@@ -22240,13 +22311,13 @@
       <c r="K4" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M4" s="30">
-        <f>ANALISI!C50</f>
-        <v>2.5</v>
+      <c r="M4" s="27">
+        <f>ANALISI!C52</f>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N4" s="27" cm="1">
         <f t="array" ref="N4">GetEfficienza(B$2,O4,M4)</f>
-        <v>0.70497948562500012</v>
+        <v>0.64918452669368176</v>
       </c>
       <c r="O4" s="27">
         <v>0.5</v>
@@ -22281,13 +22352,13 @@
         <f t="array" ref="K5">GetEfficienza(K$2,K$3,J5)</f>
         <v>0.48549555999999999</v>
       </c>
-      <c r="M5" s="28">
+      <c r="M5" s="37">
         <f>M4</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N5" s="28" cm="1">
         <f t="array" ref="N5">GetEfficienza(B$2,O5,M5)</f>
-        <v>0.61116133249999993</v>
+        <v>0.56502372001094692</v>
       </c>
       <c r="O5" s="28">
         <v>1</v>
@@ -22322,13 +22393,13 @@
         <f t="array" ref="K6">GetEfficienza(K$2,K$3,J6)</f>
         <v>0.46223731643607391</v>
       </c>
-      <c r="M6" s="30">
+      <c r="M6" s="27">
         <f>M5</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N6" s="27" cm="1">
         <f t="array" ref="N6">GetEfficienza(B$2,O6,M6)</f>
-        <v>0.40615135874999991</v>
+        <v>0.37593982270042831</v>
       </c>
       <c r="O6" s="27">
         <v>1.5</v>
@@ -22363,13 +22434,13 @@
         <f t="array" ref="K7">GetEfficienza(K$2,K$3,J7)</f>
         <v>0.44025124300904483</v>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="37">
         <f>M5</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N7" s="28" cm="1">
         <f t="array" ref="N7">GetEfficienza(B$2,O7,M7)</f>
-        <v>0.30604324999999999</v>
+        <v>0.28315113907235595</v>
       </c>
       <c r="O7" s="28">
         <v>2</v>
@@ -22937,20 +23008,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Y1" s="3"/>
@@ -22972,33 +23043,33 @@
     </row>
     <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B2">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E2">
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H2">
         <v>4</v>
       </c>
       <c r="J2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="K2">
         <v>4</v>
       </c>
-      <c r="M2" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="N2" s="45"/>
+      <c r="M2" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="N2" s="41"/>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -23026,7 +23097,7 @@
         <v>2</v>
       </c>
       <c r="M3" s="26" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="N3" s="26" t="s">
         <v>96</v>
@@ -23037,10 +23108,10 @@
     </row>
     <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>85</v>
@@ -23062,13 +23133,13 @@
       <c r="K4" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M4" s="30">
-        <f>ANALISI!C50</f>
-        <v>2.5</v>
+      <c r="M4" s="27">
+        <f>ANALISI!C52</f>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N4" s="27" cm="1">
         <f t="array" ref="N4">GetEfficienza(B$2,O4,M4)</f>
-        <v>0.69403893906250014</v>
+        <v>0.64122391789387723</v>
       </c>
       <c r="O4" s="27">
         <v>0.5</v>
@@ -23103,13 +23174,13 @@
         <f t="array" ref="K5">GetEfficienza(K$2,K$3,J5)</f>
         <v>0.48646903505242445</v>
       </c>
-      <c r="M5" s="28">
+      <c r="M5" s="37">
         <f>M4</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N5" s="28" cm="1">
         <f t="array" ref="N5">GetEfficienza(B$2,O5,M5)</f>
-        <v>0.60852397999999996</v>
+        <v>0.56308025213927571</v>
       </c>
       <c r="O5" s="28">
         <v>1</v>
@@ -23144,13 +23215,13 @@
         <f t="array" ref="K6">GetEfficienza(K$2,K$3,J6)</f>
         <v>0.4697844823961157</v>
       </c>
-      <c r="M6" s="30">
+      <c r="M6" s="27">
         <f>M5</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N6" s="27" cm="1">
         <f t="array" ref="N6">GetEfficienza(B$2,O6,M6)</f>
-        <v>0.406518555</v>
+        <v>0.37590754473629984</v>
       </c>
       <c r="O6" s="27">
         <v>1.5</v>
@@ -23185,13 +23256,13 @@
         <f t="array" ref="K7">GetEfficienza(K$2,K$3,J7)</f>
         <v>0.45396406630847214</v>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="37">
         <f>M5</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="N7" s="28" cm="1">
         <f t="array" ref="N7">GetEfficienza(B$2,O7,M7)</f>
-        <v>0.30491350874999995</v>
+        <v>0.28178203807144114</v>
       </c>
       <c r="O7" s="28">
         <v>2</v>
@@ -23845,14 +23916,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="S1" s="3"/>
@@ -23874,21 +23945,21 @@
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="G2" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="45"/>
+      <c r="G2" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="H2" s="41"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -23904,7 +23975,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="H3" s="26" t="s">
         <v>96</v>
@@ -23915,24 +23986,24 @@
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>81</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>81</v>
       </c>
       <c r="G4" s="27">
-        <f>ANALISI!C50</f>
-        <v>2.5</v>
+        <f>ANALISI!C52</f>
+        <v>2.8284271247461903</v>
       </c>
       <c r="H4" s="27" cm="1">
         <f t="array" ref="H4">gett("T50",E$2,I$4,G4)</f>
-        <v>5.3837298147770163E-2</v>
+        <v>5.7036767641874646E-2</v>
       </c>
       <c r="I4" s="27">
         <v>0.5</v>
@@ -23953,13 +24024,13 @@
         <f t="array" ref="E5">gett("T50",E$2,E$3,D5)</f>
         <v>2.33037679932865E-3</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="37">
         <f>G4</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="H5" s="28" cm="1">
         <f t="array" ref="H5">gett("T50",E$2,I$5,G5)</f>
-        <v>7.6393315101689729E-2</v>
+        <v>8.0309867313937494E-2</v>
       </c>
       <c r="I5" s="28">
         <v>1</v>
@@ -24390,14 +24461,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="S1" s="3"/>
@@ -24419,21 +24490,21 @@
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="G2" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="45"/>
+      <c r="G2" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="H2" s="41"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -24449,7 +24520,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="H3" s="26" t="s">
         <v>96</v>
@@ -24460,24 +24531,24 @@
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>82</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>82</v>
       </c>
       <c r="G4" s="27">
-        <f>ANALISI!C50</f>
-        <v>2.5</v>
+        <f>ANALISI!C52</f>
+        <v>2.8284271247461903</v>
       </c>
       <c r="H4" s="27" cm="1">
         <f t="array" ref="H4">gett("T90",E$2,I$4,G4)</f>
-        <v>0.44054769468300675</v>
+        <v>0.48711498953969745</v>
       </c>
       <c r="I4" s="27">
         <v>0.5</v>
@@ -24500,11 +24571,11 @@
       </c>
       <c r="G5" s="28">
         <f>G4</f>
-        <v>2.5</v>
+        <v>2.8284271247461903</v>
       </c>
       <c r="H5" s="28" cm="1">
         <f t="array" ref="H5">gett("T90",E$2,I$5,G5)</f>
-        <v>0.48537651044101932</v>
+        <v>0.52593193263720761</v>
       </c>
       <c r="I5" s="28">
         <v>1</v>

--- a/articolo_06_trincee-drenanti-foglio/Trincee_Drenanti_v1_0.xlsx
+++ b/articolo_06_trincee-drenanti-foglio/Trincee_Drenanti_v1_0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\_Francisco\_GitHub\franciscojmendez_Risorse\articolo_06_trincee-drenanti-foglio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFC41C7F-C839-499C-9667-33EFC263F3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96123876-38DF-4626-8043-FB78D78BDB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{3C2956EA-F146-457E-A9D7-5BDD1E22F3AE}"/>
   </bookViews>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="136">
   <si>
     <t>Trincee Drenanti - Dimensionamento di Massima</t>
   </si>
@@ -502,7 +502,7 @@
     <t>S*/H0</t>
   </si>
   <si>
-    <t>S* di progetto =  S / H0 × √(kv/kh)</t>
+    <t>S* di progetto /H0 =  S / H0 × √(kv/kh)</t>
   </si>
 </sst>
 </file>
@@ -781,7 +781,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -859,12 +859,6 @@
     <xf numFmtId="11" fontId="15" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -874,14 +868,10 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -896,11 +886,18 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -17258,12 +17255,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="44" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B3" s="42"/>
+      <c r="B3" s="44"/>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B5" s="13" t="s">
@@ -17443,20 +17440,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Y1" s="3"/>
@@ -17501,10 +17498,10 @@
       <c r="K2">
         <v>2.5</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="M2" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="N2" s="41"/>
+      <c r="N2" s="47"/>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -17568,7 +17565,7 @@
       <c r="K4" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="36">
         <f>ANALISI!C52</f>
         <v>2.8284271247461903</v>
       </c>
@@ -17609,7 +17606,7 @@
         <f t="array" ref="K5">gett("T50",K$2,K$3,J5)</f>
         <v>0.88201604018118962</v>
       </c>
-      <c r="M5" s="39">
+      <c r="M5" s="37">
         <f>M4</f>
         <v>2.8284271247461903</v>
       </c>
@@ -17650,7 +17647,7 @@
         <f t="array" ref="K6">gett("T50",K$2,K$3,J6)</f>
         <v>0.93693255230490624</v>
       </c>
-      <c r="M6" s="38">
+      <c r="M6" s="36">
         <f>M5</f>
         <v>2.8284271247461903</v>
       </c>
@@ -17691,7 +17688,7 @@
         <f t="array" ref="K7">gett("T50",K$2,K$3,J7)</f>
         <v>1.018478290239208</v>
       </c>
-      <c r="M7" s="39">
+      <c r="M7" s="37">
         <f>M6</f>
         <v>2.8284271247461903</v>
       </c>
@@ -18354,20 +18351,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Y1" s="3"/>
@@ -18412,10 +18409,10 @@
       <c r="K2">
         <v>2.5</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="M2" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="N2" s="41"/>
+      <c r="N2" s="47"/>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -18520,7 +18517,7 @@
         <f t="array" ref="K5">gett("T90",K$2,K$3,J5)</f>
         <v>2.7673687278347439</v>
       </c>
-      <c r="M5" s="37">
+      <c r="M5" s="35">
         <f>M4</f>
         <v>2.8284271247461903</v>
       </c>
@@ -18602,7 +18599,7 @@
         <f t="array" ref="K7">gett("T90",K$2,K$3,J7)</f>
         <v>3.0512167429087724</v>
       </c>
-      <c r="M7" s="37">
+      <c r="M7" s="35">
         <f>M6</f>
         <v>2.8284271247461903</v>
       </c>
@@ -19307,12 +19304,12 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19321,10 +19318,10 @@
       <c r="B3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="41"/>
+      <c r="F3" s="47"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -19528,12 +19525,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="12"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -19544,12 +19541,12 @@
       <c r="E2" s="12"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
       <c r="E3" s="12"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -19690,12 +19687,12 @@
       <c r="E14" s="12"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="43" t="s">
+      <c r="A15" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
       <c r="E15" s="12"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -19778,12 +19775,12 @@
       <c r="E21" s="12"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
       <c r="E22" s="12"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -19835,12 +19832,12 @@
       <c r="E26" s="12"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
       <c r="E27" s="12"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -19896,12 +19893,12 @@
       <c r="E31" s="12"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
       <c r="E32" s="12"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -19991,27 +19988,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="18" x14ac:dyDescent="0.25">
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="P2" s="2"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
       <c r="Q3" s="4"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
@@ -20406,14 +20403,14 @@
       <c r="M25" s="4"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
@@ -20423,12 +20420,12 @@
         <f>DATI_INPUT!$B$23</f>
         <v>1.3</v>
       </c>
-      <c r="D29" s="44" t="s">
+      <c r="D29" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
@@ -20438,12 +20435,12 @@
         <f>mesi_target</f>
         <v>6</v>
       </c>
-      <c r="D30" s="44" t="s">
+      <c r="D30" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
@@ -20453,22 +20450,22 @@
         <f>"F ≥ "&amp;F_short&amp;" raggiunto entro "&amp;DATI_INPUT!$B$25&amp;" mesi "</f>
         <v xml:space="preserve">F ≥ 1,1 raggiunto entro 6 mesi </v>
       </c>
-      <c r="D31" s="44" t="s">
+      <c r="D31" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
@@ -20478,12 +20475,12 @@
         <f>IFERROR(GetFZ(D_piano,dw_init,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
         <v>0.95706292485134314</v>
       </c>
-      <c r="D35" s="44" t="s">
+      <c r="D35" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
@@ -20493,12 +20490,12 @@
         <f>IFERROR(GetFZ(D_piano,dw_dry,c_eff,phi_eff,gamma,gammaw,beta),"-&gt; importa ModuloTrincee.bas")</f>
         <v>1.5937531595749261</v>
       </c>
-      <c r="D36" s="44" t="s">
+      <c r="D36" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="41"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
@@ -20508,12 +20505,12 @@
         <f>C29-C35</f>
         <v>0.3429370751486569</v>
       </c>
-      <c r="D37" s="44" t="s">
+      <c r="D37" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
@@ -20523,12 +20520,12 @@
         <f>C36-C35</f>
         <v>0.63669023472358299</v>
       </c>
-      <c r="D38" s="44" t="s">
+      <c r="D38" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="45"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
@@ -20538,22 +20535,22 @@
         <f>C37/C38</f>
         <v>0.53862468190287527</v>
       </c>
-      <c r="D39" s="44" t="s">
+      <c r="D39" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="41"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B41" s="48" t="s">
+      <c r="B41" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
@@ -20563,18 +20560,18 @@
         <f>DATI_INPUT!$B$28&amp;" / "&amp;DATI_INPUT!$B$29</f>
         <v>1,5 / 1</v>
       </c>
-      <c r="D43" s="44" t="s">
+      <c r="D43" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="E43" s="45"/>
-      <c r="F43" s="45"/>
-      <c r="G43" s="45"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="45" t="s">
+      <c r="B44" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="C44" s="45"/>
+      <c r="C44" s="41"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
@@ -20586,12 +20583,12 @@
     IFERROR(getsuh0(n_cfg,d_cfg,C39),"-&gt; importa ModuloTrincee.bas"))</f>
         <v>2.9446791221275923</v>
       </c>
-      <c r="D45" s="44" t="s">
+      <c r="D45" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E45" s="45"/>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="41"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
@@ -20601,12 +20598,12 @@
         <f>IF(ISNUMBER(C45),C45*H0,C45)</f>
         <v>17.668074732765554</v>
       </c>
-      <c r="D46" s="35" t="s">
+      <c r="D46" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="48"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
@@ -20616,12 +20613,12 @@
         <f>C46*SQRT(kh/kv)</f>
         <v>24.986430908098445</v>
       </c>
-      <c r="D47" s="44" t="s">
+      <c r="D47" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B48" s="22"/>
@@ -20632,10 +20629,10 @@
       <c r="G48" s="22"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="45" t="s">
+      <c r="B49" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="C49" s="45"/>
+      <c r="C49" s="41"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
@@ -20644,12 +20641,12 @@
       <c r="C50" s="9">
         <v>24</v>
       </c>
-      <c r="D50" s="44" t="s">
+      <c r="D50" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E50" s="45"/>
-      <c r="F50" s="45"/>
-      <c r="G50" s="45"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
@@ -20659,12 +20656,12 @@
         <f>IFERROR(C50/H0,"")</f>
         <v>4</v>
       </c>
-      <c r="D51" s="44" t="s">
+      <c r="D51" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
-      <c r="G51" s="45"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="41"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
@@ -20674,10 +20671,12 @@
         <f>C51*SQRT(kv/kh)</f>
         <v>2.8284271247461903</v>
       </c>
-      <c r="D52" s="35"/>
-      <c r="E52" s="36"/>
-      <c r="F52" s="36"/>
-      <c r="G52" s="36"/>
+      <c r="D52" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="E52" s="48"/>
+      <c r="F52" s="48"/>
+      <c r="G52" s="48"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
@@ -20689,12 +20688,12 @@
     IFERROR(GetEfficienza(n_cfg,d_cfg,C52),"-&gt; importa ModuloTrincee.bas"))</f>
         <v>0.55499293199886912</v>
       </c>
-      <c r="D53" s="44" t="s">
+      <c r="D53" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E53" s="45"/>
-      <c r="F53" s="45"/>
-      <c r="G53" s="45"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="41"/>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
@@ -20704,20 +20703,20 @@
         <f>IF(OR(NOT(ISNUMBER(C53)),NOT(ISNUMBER(C39))),"-&gt; importa ModuloTrincee.bas",IF(C53&gt;=C39,"VERIFICATO: interasse scelto soddisfa F_target","NON VERIFICATO: ridurre interasse o rivedere F_target"))</f>
         <v>VERIFICATO: interasse scelto soddisfa F_target</v>
       </c>
-      <c r="D54" s="46"/>
-      <c r="E54" s="47"/>
-      <c r="F54" s="47"/>
-      <c r="G54" s="47"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B56" s="48" t="s">
+      <c r="B56" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="C56" s="48"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
+      <c r="C56" s="39"/>
+      <c r="D56" s="39"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="39"/>
+      <c r="G56" s="39"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
@@ -20729,12 +20728,12 @@
     IFERROR(gett("T50",n_tempi,d_cfg,C52),"-&gt; importa ModuloTrincee.bas"))</f>
         <v>0.22109748867241455</v>
       </c>
-      <c r="D58" s="44" t="s">
+      <c r="D58" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E58" s="45"/>
-      <c r="F58" s="45"/>
-      <c r="G58" s="45"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="41"/>
+      <c r="G58" s="41"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
@@ -20746,12 +20745,12 @@
     IFERROR(gett("T90",n_tempi,d_cfg,C52),"-&gt; importa ModuloTrincee.bas"))</f>
         <v>2.9288989432352714</v>
       </c>
-      <c r="D59" s="44" t="s">
+      <c r="D59" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E59" s="45"/>
-      <c r="F59" s="45"/>
-      <c r="G59" s="45"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="41"/>
+      <c r="G59" s="41"/>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
@@ -20761,12 +20760,12 @@
         <f>IFERROR(C58*(2*(1+nu)*(1-2*nu)*gammaw*H0^2)/(Emod*kv)/(30*86400),"")</f>
         <v>5.0207554719360807</v>
       </c>
-      <c r="D60" s="44" t="s">
+      <c r="D60" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="E60" s="45"/>
-      <c r="F60" s="45"/>
-      <c r="G60" s="45"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="41"/>
+      <c r="G60" s="41"/>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
@@ -20776,12 +20775,12 @@
         <f>IFERROR(C59*(2*(1+nu)*(1-2*nu)*gammaw*H0^2)/(Emod*kv)/(30*86400),"")</f>
         <v>66.510413502634279</v>
       </c>
-      <c r="D61" s="44" t="s">
+      <c r="D61" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="E61" s="45"/>
-      <c r="F61" s="45"/>
-      <c r="G61" s="45"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="41"/>
+      <c r="G61" s="41"/>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
@@ -20791,12 +20790,12 @@
         <f>IFERROR(C53*C38,"")</f>
         <v>0.3533585801442895</v>
       </c>
-      <c r="D62" s="44" t="s">
+      <c r="D62" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E62" s="45"/>
-      <c r="F62" s="45"/>
-      <c r="G62" s="45"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="41"/>
+      <c r="G62" s="41"/>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
@@ -20806,12 +20805,12 @@
         <f>IFERROR(C35+C62,"")</f>
         <v>1.3104215049956327</v>
       </c>
-      <c r="D63" s="44" t="s">
+      <c r="D63" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E63" s="45"/>
-      <c r="F63" s="45"/>
-      <c r="G63" s="45"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="41"/>
+      <c r="G63" s="41"/>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
@@ -20821,12 +20820,12 @@
         <f>IFERROR(C35+0.5*C62,"")</f>
         <v>1.1337422149234879</v>
       </c>
-      <c r="D64" s="44" t="s">
+      <c r="D64" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E64" s="45"/>
-      <c r="F64" s="45"/>
-      <c r="G64" s="45"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="41"/>
+      <c r="G64" s="41"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
@@ -20836,12 +20835,12 @@
         <f>IFERROR(C35+0.9*C62,"")</f>
         <v>1.2750856469812037</v>
       </c>
-      <c r="D65" s="44" t="s">
+      <c r="D65" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E65" s="45"/>
-      <c r="F65" s="45"/>
-      <c r="G65" s="45"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="41"/>
+      <c r="G65" s="41"/>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
@@ -20854,14 +20853,14 @@
       <c r="D66" s="3"/>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B68" s="48" t="s">
+      <c r="B68" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="48"/>
-      <c r="D68" s="48"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="48"/>
-      <c r="G68" s="48"/>
+      <c r="C68" s="39"/>
+      <c r="D68" s="39"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="39"/>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
@@ -20871,12 +20870,12 @@
         <f>IFERROR(C50*SQRT(DATI_INPUT!$B$11/DATI_INPUT!$B$10)/(2*DATI_INPUT!$B$6),"")</f>
         <v>1.4142135623730951</v>
       </c>
-      <c r="D70" s="44" t="s">
+      <c r="D70" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E70" s="45"/>
-      <c r="F70" s="45"/>
-      <c r="G70" s="45"/>
+      <c r="E70" s="41"/>
+      <c r="F70" s="41"/>
+      <c r="G70" s="41"/>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
@@ -20888,12 +20887,12 @@
     IFERROR(getqadim(C70),"-&gt; importa ModuloTrincee.bas"))</f>
         <v>1.4529920652750568</v>
       </c>
-      <c r="D71" s="44" t="s">
+      <c r="D71" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E71" s="45"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="45"/>
+      <c r="E71" s="41"/>
+      <c r="F71" s="41"/>
+      <c r="G71" s="41"/>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
@@ -20903,12 +20902,12 @@
         <f>IFERROR(C71*DATI_INPUT!$B$11*DATI_INPUT!$B$6*1000*3600,"")</f>
         <v>9.4153885829823675E-2</v>
       </c>
-      <c r="D72" s="44" t="s">
+      <c r="D72" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="E72" s="45"/>
-      <c r="F72" s="45"/>
-      <c r="G72" s="45"/>
+      <c r="E72" s="41"/>
+      <c r="F72" s="41"/>
+      <c r="G72" s="41"/>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
@@ -20918,28 +20917,26 @@
         <f>IFERROR(C72*DATI_INPUT!$B$33,"")</f>
         <v>4.7076942914911841</v>
       </c>
-      <c r="D73" s="44" t="s">
+      <c r="D73" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="E73" s="45"/>
-      <c r="F73" s="45"/>
-      <c r="G73" s="45"/>
+      <c r="E73" s="41"/>
+      <c r="F73" s="41"/>
+      <c r="G73" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B41:G41"/>
-    <mergeCell ref="D38:G38"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="D30:G30"/>
+  <mergeCells count="38">
+    <mergeCell ref="D53:G53"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="D50:G50"/>
+    <mergeCell ref="D51:G51"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="D46:G46"/>
     <mergeCell ref="D71:G71"/>
     <mergeCell ref="D72:G72"/>
     <mergeCell ref="D73:G73"/>
@@ -20954,15 +20951,19 @@
     <mergeCell ref="D70:G70"/>
     <mergeCell ref="D64:G64"/>
     <mergeCell ref="D65:G65"/>
-    <mergeCell ref="D53:G53"/>
-    <mergeCell ref="D54:G54"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D43:G43"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D47:G47"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="D51:G51"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="D30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -20984,14 +20985,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="S1" s="3"/>
@@ -21024,10 +21025,10 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="H2" s="41"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -21092,7 +21093,7 @@
         <f t="array" ref="E5">GetEfficienza(E$2,E$3,D5)</f>
         <v>0.81994611200393552</v>
       </c>
-      <c r="G5" s="37">
+      <c r="G5" s="35">
         <f>G4</f>
         <v>2.8284271247461903</v>
       </c>
@@ -21523,17 +21524,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="V1" s="3"/>
@@ -21572,10 +21573,10 @@
       <c r="H2">
         <v>1.5</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="J2" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="K2" s="41"/>
+      <c r="K2" s="47"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -21660,7 +21661,7 @@
         <f t="array" ref="H5">GetEfficienza(H$2,H$3,G5)</f>
         <v>0.64772029102682993</v>
       </c>
-      <c r="J5" s="37">
+      <c r="J5" s="35">
         <f>J4</f>
         <v>2.8284271247461903</v>
       </c>
@@ -22186,20 +22187,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Y1" s="3"/>
@@ -22244,10 +22245,10 @@
       <c r="K2">
         <v>2.5</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="M2" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="N2" s="41"/>
+      <c r="N2" s="47"/>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -22352,7 +22353,7 @@
         <f t="array" ref="K5">GetEfficienza(K$2,K$3,J5)</f>
         <v>0.48549555999999999</v>
       </c>
-      <c r="M5" s="37">
+      <c r="M5" s="35">
         <f>M4</f>
         <v>2.8284271247461903</v>
       </c>
@@ -22434,7 +22435,7 @@
         <f t="array" ref="K7">GetEfficienza(K$2,K$3,J7)</f>
         <v>0.44025124300904483</v>
       </c>
-      <c r="M7" s="37">
+      <c r="M7" s="35">
         <f>M5</f>
         <v>2.8284271247461903</v>
       </c>
@@ -23008,20 +23009,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Y1" s="3"/>
@@ -23066,10 +23067,10 @@
       <c r="K2">
         <v>4</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="M2" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="N2" s="41"/>
+      <c r="N2" s="47"/>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -23174,7 +23175,7 @@
         <f t="array" ref="K5">GetEfficienza(K$2,K$3,J5)</f>
         <v>0.48646903505242445</v>
       </c>
-      <c r="M5" s="37">
+      <c r="M5" s="35">
         <f>M4</f>
         <v>2.8284271247461903</v>
       </c>
@@ -23256,7 +23257,7 @@
         <f t="array" ref="K7">GetEfficienza(K$2,K$3,J7)</f>
         <v>0.45396406630847214</v>
       </c>
-      <c r="M7" s="37">
+      <c r="M7" s="35">
         <f>M5</f>
         <v>2.8284271247461903</v>
       </c>
@@ -23916,14 +23917,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="S1" s="3"/>
@@ -23956,10 +23957,10 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="H2" s="41"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -24024,7 +24025,7 @@
         <f t="array" ref="E5">gett("T50",E$2,E$3,D5)</f>
         <v>2.33037679932865E-3</v>
       </c>
-      <c r="G5" s="37">
+      <c r="G5" s="35">
         <f>G4</f>
         <v>2.8284271247461903</v>
       </c>
@@ -24461,14 +24462,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="S1" s="3"/>
@@ -24501,10 +24502,10 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="H2" s="41"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
